--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDF8FA71-0FE8-4F54-8131-BF27B41E3E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{701D84C6-0EB0-44F2-A1E9-9FC80D98B122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3154,7 +3154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470743F4-1540-4CA7-B765-6CB1F2A1A424}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E2E7F7-0A6D-43ED-BE08-4971ACC2D8D8}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12499,7 +12499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED631B4-B65D-4106-BDE3-650EF0794E79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57709C5D-0DD2-4E30-8D0F-6B6A14A4356D}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{701D84C6-0EB0-44F2-A1E9-9FC80D98B122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A80CA368-DAA0-46D9-BEC1-E4BBF51981DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3154,7 +3154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E2E7F7-0A6D-43ED-BE08-4971ACC2D8D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4C81A76-BD5F-4ACF-AF5C-883C67DBDFB4}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12499,7 +12499,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57709C5D-0DD2-4E30-8D0F-6B6A14A4356D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B22802DD-755A-4102-91B8-66847BE19B7A}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78F450BB-0C18-480B-928F-5B1825C973A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE7BBF4C-2437-4E7E-939F-A9D5BA12BB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3773" uniqueCount="840">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -334,9 +334,6 @@
     <t>Hydropower - large-scale unit</t>
   </si>
   <si>
-    <t>ISO</t>
-  </si>
-  <si>
     <t>Solar Low</t>
   </si>
   <si>
@@ -392,9 +389,6 @@
   </si>
   <si>
     <t>\I: hydro</t>
-  </si>
-  <si>
-    <t>SGP</t>
   </si>
   <si>
     <t>UCE_min oil fleet utilization</t>
@@ -490,6 +484,15 @@
     <t>share_of_generation_pct</t>
   </si>
   <si>
+    <t>BUILD RATE ASSUMPTIONS</t>
+  </si>
+  <si>
+    <t>iso</t>
+  </si>
+  <si>
+    <t>ZAF</t>
+  </si>
+  <si>
     <t>pasti</t>
   </si>
   <si>
@@ -1208,9 +1211,6 @@
   </si>
   <si>
     <t>region</t>
-  </si>
-  <si>
-    <t>ZAF</t>
   </si>
   <si>
     <t>Bioenergy + CCUS_w836844162-400_ZAF</t>
@@ -2784,7 +2784,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2797,9 +2797,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3142,7 +3139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442B9F56-1EBF-47C4-8B9C-74BB7B45B3AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97870A7-AF66-45E8-BF7F-3FE6D95B5BA1}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3151,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="2:32" x14ac:dyDescent="0.45">
@@ -3165,25 +3162,25 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H3" t="s">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L3" t="s">
         <v>14</v>
@@ -3192,30 +3189,30 @@
         <v>3</v>
       </c>
       <c r="Q3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="R3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="U3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="V3" t="s">
         <v>3</v>
       </c>
       <c r="W3" t="s">
+        <v>307</v>
+      </c>
+      <c r="X3" t="s">
+        <v>349</v>
+      </c>
+      <c r="AA3" t="s">
         <v>306</v>
-      </c>
-      <c r="X3" t="s">
-        <v>348</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C4">
         <v>1.7874764334110815</v>
@@ -3227,31 +3224,31 @@
         <v>0.98938000000000004</v>
       </c>
       <c r="H4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J4">
         <v>0.49313052870602286</v>
       </c>
       <c r="K4" t="s">
+        <v>312</v>
+      </c>
+      <c r="L4" t="s">
         <v>311</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4" t="s">
         <v>310</v>
       </c>
-      <c r="P4" t="s">
-        <v>309</v>
-      </c>
       <c r="Q4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U4" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V4" t="s">
         <v>361</v>
@@ -3263,7 +3260,7 @@
         <v>363</v>
       </c>
       <c r="AA4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AB4" t="s">
         <v>832</v>
@@ -3283,7 +3280,7 @@
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5">
         <v>1.7874764334110815</v>
@@ -3295,31 +3292,31 @@
         <v>0.98224</v>
       </c>
       <c r="H5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J5">
         <v>0.19001775000835899</v>
       </c>
       <c r="K5" t="s">
+        <v>312</v>
+      </c>
+      <c r="L5" t="s">
         <v>311</v>
       </c>
-      <c r="L5" t="s">
-        <v>310</v>
-      </c>
       <c r="P5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q5" t="s">
+        <v>352</v>
+      </c>
+      <c r="R5" t="s">
         <v>351</v>
       </c>
-      <c r="R5" t="s">
-        <v>350</v>
-      </c>
       <c r="U5" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V5" t="s">
         <v>364</v>
@@ -3348,7 +3345,7 @@
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C6">
         <v>1.7874764334110815</v>
@@ -3360,31 +3357,31 @@
         <v>0.99729999999999996</v>
       </c>
       <c r="H6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J6">
         <v>8.0023434081469696E-2</v>
       </c>
       <c r="K6" t="s">
+        <v>312</v>
+      </c>
+      <c r="L6" t="s">
         <v>311</v>
       </c>
-      <c r="L6" t="s">
-        <v>310</v>
-      </c>
       <c r="P6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U6" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V6" t="s">
         <v>365</v>
@@ -3413,7 +3410,7 @@
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7">
         <v>3.5749528668221631</v>
@@ -3425,31 +3422,31 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="H7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J7">
         <v>6.1175745434933274E-2</v>
       </c>
       <c r="K7" t="s">
+        <v>312</v>
+      </c>
+      <c r="L7" t="s">
         <v>311</v>
       </c>
-      <c r="L7" t="s">
-        <v>310</v>
-      </c>
       <c r="P7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U7" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V7" t="s">
         <v>366</v>
@@ -3463,7 +3460,7 @@
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8">
         <v>1.7874764334110815</v>
@@ -3475,31 +3472,31 @@
         <v>0.98997999999999997</v>
       </c>
       <c r="H8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J8">
         <v>5.1036376614182213E-2</v>
       </c>
       <c r="K8" t="s">
+        <v>312</v>
+      </c>
+      <c r="L8" t="s">
         <v>311</v>
       </c>
-      <c r="L8" t="s">
-        <v>310</v>
-      </c>
       <c r="P8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U8" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V8" t="s">
         <v>367</v>
@@ -3513,7 +3510,7 @@
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9">
         <v>1.7874764334110815</v>
@@ -3525,31 +3522,31 @@
         <v>0.99970000000000003</v>
       </c>
       <c r="H9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J9">
         <v>4.2189313070315294E-2</v>
       </c>
       <c r="K9" t="s">
+        <v>312</v>
+      </c>
+      <c r="L9" t="s">
         <v>311</v>
       </c>
-      <c r="L9" t="s">
-        <v>310</v>
-      </c>
       <c r="P9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U9" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V9" t="s">
         <v>368</v>
@@ -3563,7 +3560,7 @@
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C10">
         <v>1.7874764334110815</v>
@@ -3575,31 +3572,31 @@
         <v>0.99465999999999999</v>
       </c>
       <c r="H10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J10">
         <v>3.1319068393500647E-2</v>
       </c>
       <c r="K10" t="s">
+        <v>312</v>
+      </c>
+      <c r="L10" t="s">
         <v>311</v>
       </c>
-      <c r="L10" t="s">
-        <v>310</v>
-      </c>
       <c r="P10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U10" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V10" t="s">
         <v>369</v>
@@ -3613,7 +3610,7 @@
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11">
         <v>1.7874764334110815</v>
@@ -3625,31 +3622,31 @@
         <v>0.99760000000000004</v>
       </c>
       <c r="H11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J11">
         <v>1.5652251023787294E-2</v>
       </c>
       <c r="K11" t="s">
+        <v>312</v>
+      </c>
+      <c r="L11" t="s">
         <v>311</v>
       </c>
-      <c r="L11" t="s">
-        <v>310</v>
-      </c>
       <c r="P11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U11" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V11" t="s">
         <v>370</v>
@@ -3663,7 +3660,7 @@
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12">
         <v>1.7874764334110815</v>
@@ -3675,31 +3672,31 @@
         <v>0.98763999999999996</v>
       </c>
       <c r="H12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J12">
         <v>1.545553266742933E-2</v>
       </c>
       <c r="K12" t="s">
+        <v>312</v>
+      </c>
+      <c r="L12" t="s">
         <v>311</v>
       </c>
-      <c r="L12" t="s">
-        <v>310</v>
-      </c>
       <c r="P12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q12" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U12" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V12" t="s">
         <v>371</v>
@@ -3713,7 +3710,7 @@
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13">
         <v>3.5749528668221631</v>
@@ -3725,31 +3722,31 @@
         <v>0.99490000000000001</v>
       </c>
       <c r="H13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J13">
         <v>0.49313052870602286</v>
       </c>
       <c r="K13" t="s">
+        <v>312</v>
+      </c>
+      <c r="L13" t="s">
         <v>311</v>
       </c>
-      <c r="L13" t="s">
-        <v>310</v>
-      </c>
       <c r="P13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U13" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V13" t="s">
         <v>372</v>
@@ -3763,7 +3760,7 @@
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14">
         <v>1.7874764334110815</v>
@@ -3775,31 +3772,31 @@
         <v>0.99075999999999997</v>
       </c>
       <c r="H14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J14">
         <v>0.19001775000835899</v>
       </c>
       <c r="K14" t="s">
+        <v>312</v>
+      </c>
+      <c r="L14" t="s">
         <v>311</v>
       </c>
-      <c r="L14" t="s">
-        <v>310</v>
-      </c>
       <c r="P14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q14" t="s">
+        <v>352</v>
+      </c>
+      <c r="R14" t="s">
         <v>351</v>
       </c>
-      <c r="R14" t="s">
-        <v>350</v>
-      </c>
       <c r="U14" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V14" t="s">
         <v>373</v>
@@ -3813,7 +3810,7 @@
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C15">
         <v>1.7874764334110815</v>
@@ -3825,31 +3822,31 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="H15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J15">
         <v>8.0023434081469696E-2</v>
       </c>
       <c r="K15" t="s">
+        <v>312</v>
+      </c>
+      <c r="L15" t="s">
         <v>311</v>
       </c>
-      <c r="L15" t="s">
-        <v>310</v>
-      </c>
       <c r="P15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U15" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V15" t="s">
         <v>374</v>
@@ -3863,7 +3860,7 @@
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16">
         <v>1.7874764334110815</v>
@@ -3875,31 +3872,31 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="H16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J16">
         <v>6.1175745434933274E-2</v>
       </c>
       <c r="K16" t="s">
+        <v>312</v>
+      </c>
+      <c r="L16" t="s">
         <v>311</v>
       </c>
-      <c r="L16" t="s">
-        <v>310</v>
-      </c>
       <c r="P16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U16" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V16" t="s">
         <v>375</v>
@@ -3913,7 +3910,7 @@
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C17">
         <v>1.7874764334110815</v>
@@ -3925,37 +3922,37 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="H17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J17">
         <v>5.1036376614182213E-2</v>
       </c>
       <c r="K17" t="s">
+        <v>312</v>
+      </c>
+      <c r="L17" t="s">
         <v>311</v>
       </c>
-      <c r="L17" t="s">
-        <v>310</v>
-      </c>
       <c r="P17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q17" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R17" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U17" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V17" t="s">
         <v>376</v>
       </c>
       <c r="W17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X17" t="s">
         <v>363</v>
@@ -3963,7 +3960,7 @@
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18">
         <v>1.7874764334110815</v>
@@ -3975,37 +3972,37 @@
         <v>0.99502000000000002</v>
       </c>
       <c r="H18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J18">
         <v>4.2189313070315294E-2</v>
       </c>
       <c r="K18" t="s">
+        <v>312</v>
+      </c>
+      <c r="L18" t="s">
         <v>311</v>
       </c>
-      <c r="L18" t="s">
-        <v>310</v>
-      </c>
       <c r="P18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q18" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U18" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V18" t="s">
         <v>377</v>
       </c>
       <c r="W18" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X18" t="s">
         <v>363</v>
@@ -4013,7 +4010,7 @@
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19">
         <v>1.7874764334110815</v>
@@ -4025,37 +4022,37 @@
         <v>0.99724000000000002</v>
       </c>
       <c r="H19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I19" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J19">
         <v>3.1319068393500647E-2</v>
       </c>
       <c r="K19" t="s">
+        <v>312</v>
+      </c>
+      <c r="L19" t="s">
         <v>311</v>
       </c>
-      <c r="L19" t="s">
-        <v>310</v>
-      </c>
       <c r="P19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U19" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V19" t="s">
         <v>378</v>
       </c>
       <c r="W19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X19" t="s">
         <v>363</v>
@@ -4063,7 +4060,7 @@
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20">
         <v>1.7874764334110815</v>
@@ -4075,37 +4072,37 @@
         <v>0.99736000000000002</v>
       </c>
       <c r="H20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J20">
         <v>1.5652251023787294E-2</v>
       </c>
       <c r="K20" t="s">
+        <v>312</v>
+      </c>
+      <c r="L20" t="s">
         <v>311</v>
       </c>
-      <c r="L20" t="s">
-        <v>310</v>
-      </c>
       <c r="P20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R20" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U20" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V20" t="s">
         <v>379</v>
       </c>
       <c r="W20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X20" t="s">
         <v>363</v>
@@ -4113,7 +4110,7 @@
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21">
         <v>3.5749528668221644</v>
@@ -4125,37 +4122,37 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="H21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I21" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J21">
         <v>1.545553266742933E-2</v>
       </c>
       <c r="K21" t="s">
+        <v>312</v>
+      </c>
+      <c r="L21" t="s">
         <v>311</v>
       </c>
-      <c r="L21" t="s">
-        <v>310</v>
-      </c>
       <c r="P21" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U21" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V21" t="s">
         <v>380</v>
       </c>
       <c r="W21" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X21" t="s">
         <v>363</v>
@@ -4163,7 +4160,7 @@
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22">
         <v>7.1499057336443288</v>
@@ -4175,37 +4172,37 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="H22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J22">
         <v>0.49313052870602286</v>
       </c>
       <c r="K22" t="s">
+        <v>312</v>
+      </c>
+      <c r="L22" t="s">
         <v>311</v>
       </c>
-      <c r="L22" t="s">
-        <v>310</v>
-      </c>
       <c r="P22" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q22" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U22" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V22" t="s">
         <v>381</v>
       </c>
       <c r="W22" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X22" t="s">
         <v>363</v>
@@ -4213,7 +4210,7 @@
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23">
         <v>1.7874764334110815</v>
@@ -4225,37 +4222,37 @@
         <v>0.99994000000000005</v>
       </c>
       <c r="H23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J23">
         <v>0.19001775000835899</v>
       </c>
       <c r="K23" t="s">
+        <v>312</v>
+      </c>
+      <c r="L23" t="s">
         <v>311</v>
       </c>
-      <c r="L23" t="s">
-        <v>310</v>
-      </c>
       <c r="P23" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q23" t="s">
+        <v>352</v>
+      </c>
+      <c r="R23" t="s">
         <v>351</v>
       </c>
-      <c r="R23" t="s">
-        <v>350</v>
-      </c>
       <c r="U23" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V23" t="s">
         <v>382</v>
       </c>
       <c r="W23" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X23" t="s">
         <v>363</v>
@@ -4263,7 +4260,7 @@
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C24">
         <v>3.5749528668221644</v>
@@ -4275,37 +4272,37 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="H24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I24" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J24">
         <v>8.0023434081469696E-2</v>
       </c>
       <c r="K24" t="s">
+        <v>312</v>
+      </c>
+      <c r="L24" t="s">
         <v>311</v>
       </c>
-      <c r="L24" t="s">
-        <v>310</v>
-      </c>
       <c r="P24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q24" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R24" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U24" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V24" t="s">
         <v>383</v>
       </c>
       <c r="W24" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X24" t="s">
         <v>363</v>
@@ -4313,7 +4310,7 @@
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C25">
         <v>1.7874764334110815</v>
@@ -4325,37 +4322,37 @@
         <v>0.98829999999999996</v>
       </c>
       <c r="H25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J25">
         <v>6.1175745434933274E-2</v>
       </c>
       <c r="K25" t="s">
+        <v>312</v>
+      </c>
+      <c r="L25" t="s">
         <v>311</v>
       </c>
-      <c r="L25" t="s">
-        <v>310</v>
-      </c>
       <c r="P25" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q25" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R25" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U25" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V25" t="s">
         <v>384</v>
       </c>
       <c r="W25" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X25" t="s">
         <v>363</v>
@@ -4363,7 +4360,7 @@
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C26">
         <v>1.7874764334110815</v>
@@ -4375,37 +4372,37 @@
         <v>0.99490000000000001</v>
       </c>
       <c r="H26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I26" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J26">
         <v>5.1036376614182213E-2</v>
       </c>
       <c r="K26" t="s">
+        <v>312</v>
+      </c>
+      <c r="L26" t="s">
         <v>311</v>
       </c>
-      <c r="L26" t="s">
-        <v>310</v>
-      </c>
       <c r="P26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q26" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R26" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U26" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V26" t="s">
         <v>385</v>
       </c>
       <c r="W26" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X26" t="s">
         <v>363</v>
@@ -4413,7 +4410,7 @@
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27">
         <v>1.7874764334110815</v>
@@ -4425,37 +4422,37 @@
         <v>0.98302</v>
       </c>
       <c r="H27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I27" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J27">
         <v>4.2189313070315294E-2</v>
       </c>
       <c r="K27" t="s">
+        <v>312</v>
+      </c>
+      <c r="L27" t="s">
         <v>311</v>
       </c>
-      <c r="L27" t="s">
-        <v>310</v>
-      </c>
       <c r="P27" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q27" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U27" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V27" t="s">
         <v>386</v>
       </c>
       <c r="W27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X27" t="s">
         <v>363</v>
@@ -4463,7 +4460,7 @@
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C28">
         <v>1.7874764334110815</v>
@@ -4475,37 +4472,37 @@
         <v>0.99927999999999995</v>
       </c>
       <c r="H28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I28" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J28">
         <v>3.1319068393500647E-2</v>
       </c>
       <c r="K28" t="s">
+        <v>312</v>
+      </c>
+      <c r="L28" t="s">
         <v>311</v>
       </c>
-      <c r="L28" t="s">
-        <v>310</v>
-      </c>
       <c r="P28" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q28" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U28" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V28" t="s">
         <v>387</v>
       </c>
       <c r="W28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X28" t="s">
         <v>363</v>
@@ -4513,7 +4510,7 @@
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C29">
         <v>1.7874764334110815</v>
@@ -4525,37 +4522,37 @@
         <v>0.99250000000000005</v>
       </c>
       <c r="H29" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J29">
         <v>1.5652251023787294E-2</v>
       </c>
       <c r="K29" t="s">
+        <v>312</v>
+      </c>
+      <c r="L29" t="s">
         <v>311</v>
       </c>
-      <c r="L29" t="s">
-        <v>310</v>
-      </c>
       <c r="P29" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R29" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U29" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V29" t="s">
         <v>388</v>
       </c>
       <c r="W29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X29" t="s">
         <v>363</v>
@@ -4563,7 +4560,7 @@
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C30">
         <v>3.5749528668221631</v>
@@ -4575,37 +4572,37 @@
         <v>0.99922</v>
       </c>
       <c r="H30" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I30" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J30">
         <v>1.545553266742933E-2</v>
       </c>
       <c r="K30" t="s">
+        <v>312</v>
+      </c>
+      <c r="L30" t="s">
         <v>311</v>
       </c>
-      <c r="L30" t="s">
-        <v>310</v>
-      </c>
       <c r="P30" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U30" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V30" t="s">
         <v>389</v>
       </c>
       <c r="W30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X30" t="s">
         <v>363</v>
@@ -4613,7 +4610,7 @@
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C31">
         <v>3.5749528668221631</v>
@@ -4625,37 +4622,37 @@
         <v>0.99346000000000001</v>
       </c>
       <c r="H31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I31" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J31">
         <v>0.49313052870602286</v>
       </c>
       <c r="K31" t="s">
+        <v>312</v>
+      </c>
+      <c r="L31" t="s">
         <v>311</v>
       </c>
-      <c r="L31" t="s">
-        <v>310</v>
-      </c>
       <c r="P31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="R31" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U31" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V31" t="s">
         <v>390</v>
       </c>
       <c r="W31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X31" t="s">
         <v>363</v>
@@ -4663,7 +4660,7 @@
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32">
         <v>1.7874764334110815</v>
@@ -4675,37 +4672,37 @@
         <v>0.99387999999999999</v>
       </c>
       <c r="H32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I32" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J32">
         <v>0.19001775000835899</v>
       </c>
       <c r="K32" t="s">
+        <v>312</v>
+      </c>
+      <c r="L32" t="s">
         <v>311</v>
       </c>
-      <c r="L32" t="s">
-        <v>310</v>
-      </c>
       <c r="P32" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q32" t="s">
+        <v>352</v>
+      </c>
+      <c r="R32" t="s">
         <v>351</v>
       </c>
-      <c r="R32" t="s">
-        <v>350</v>
-      </c>
       <c r="U32" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V32" t="s">
         <v>391</v>
       </c>
       <c r="W32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X32" t="s">
         <v>363</v>
@@ -4713,7 +4710,7 @@
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33">
         <v>1.7874764334110815</v>
@@ -4725,37 +4722,37 @@
         <v>0.98956</v>
       </c>
       <c r="H33" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J33">
         <v>8.0023434081469696E-2</v>
       </c>
       <c r="K33" t="s">
+        <v>312</v>
+      </c>
+      <c r="L33" t="s">
         <v>311</v>
       </c>
-      <c r="L33" t="s">
-        <v>310</v>
-      </c>
       <c r="P33" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q33" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R33" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U33" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V33" t="s">
         <v>392</v>
       </c>
       <c r="W33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X33" t="s">
         <v>363</v>
@@ -4763,7 +4760,7 @@
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C34">
         <v>3.5749528668221631</v>
@@ -4775,37 +4772,37 @@
         <v>0.98973999999999995</v>
       </c>
       <c r="H34" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J34">
         <v>6.1175745434933274E-2</v>
       </c>
       <c r="K34" t="s">
+        <v>312</v>
+      </c>
+      <c r="L34" t="s">
         <v>311</v>
       </c>
-      <c r="L34" t="s">
-        <v>310</v>
-      </c>
       <c r="P34" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q34" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U34" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V34" t="s">
         <v>393</v>
       </c>
       <c r="W34" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X34" t="s">
         <v>363</v>
@@ -4813,7 +4810,7 @@
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C35">
         <v>1.7874764334110815</v>
@@ -4825,37 +4822,37 @@
         <v>0.99561999999999995</v>
       </c>
       <c r="H35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J35">
         <v>5.1036376614182213E-2</v>
       </c>
       <c r="K35" t="s">
+        <v>312</v>
+      </c>
+      <c r="L35" t="s">
         <v>311</v>
       </c>
-      <c r="L35" t="s">
-        <v>310</v>
-      </c>
       <c r="P35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q35" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R35" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U35" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V35" t="s">
         <v>394</v>
       </c>
       <c r="W35" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X35" t="s">
         <v>363</v>
@@ -4863,7 +4860,7 @@
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C36">
         <v>3.5749528668221631</v>
@@ -4875,37 +4872,37 @@
         <v>0.99580000000000002</v>
       </c>
       <c r="H36" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I36" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J36">
         <v>4.2189313070315294E-2</v>
       </c>
       <c r="K36" t="s">
+        <v>312</v>
+      </c>
+      <c r="L36" t="s">
         <v>311</v>
       </c>
-      <c r="L36" t="s">
-        <v>310</v>
-      </c>
       <c r="P36" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q36" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R36" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U36" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V36" t="s">
         <v>395</v>
       </c>
       <c r="W36" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X36" t="s">
         <v>363</v>
@@ -4913,7 +4910,7 @@
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C37">
         <v>1.7874764334110815</v>
@@ -4925,37 +4922,37 @@
         <v>0.9919</v>
       </c>
       <c r="H37" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J37">
         <v>3.1319068393500647E-2</v>
       </c>
       <c r="K37" t="s">
+        <v>312</v>
+      </c>
+      <c r="L37" t="s">
         <v>311</v>
       </c>
-      <c r="L37" t="s">
-        <v>310</v>
-      </c>
       <c r="P37" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q37" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R37" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U37" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V37" t="s">
         <v>396</v>
       </c>
       <c r="W37" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X37" t="s">
         <v>363</v>
@@ -4963,7 +4960,7 @@
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C38">
         <v>1.7874764334110815</v>
@@ -4975,37 +4972,37 @@
         <v>0.99094000000000004</v>
       </c>
       <c r="H38" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I38" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J38">
         <v>1.5652251023787294E-2</v>
       </c>
       <c r="K38" t="s">
+        <v>312</v>
+      </c>
+      <c r="L38" t="s">
         <v>311</v>
       </c>
-      <c r="L38" t="s">
-        <v>310</v>
-      </c>
       <c r="P38" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q38" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R38" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U38" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V38" t="s">
         <v>397</v>
       </c>
       <c r="W38" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X38" t="s">
         <v>363</v>
@@ -5013,7 +5010,7 @@
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C39">
         <v>1.7874764334110815</v>
@@ -5025,37 +5022,37 @@
         <v>0.99502000000000002</v>
       </c>
       <c r="H39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I39" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J39">
         <v>1.545553266742933E-2</v>
       </c>
       <c r="K39" t="s">
+        <v>312</v>
+      </c>
+      <c r="L39" t="s">
         <v>311</v>
       </c>
-      <c r="L39" t="s">
-        <v>310</v>
-      </c>
       <c r="P39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q39" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="U39" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V39" t="s">
         <v>398</v>
       </c>
       <c r="W39" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X39" t="s">
         <v>363</v>
@@ -5063,7 +5060,7 @@
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C40">
         <v>1.7874764334110815</v>
@@ -5075,13 +5072,13 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="U40" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V40" t="s">
         <v>399</v>
       </c>
       <c r="W40" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X40" t="s">
         <v>363</v>
@@ -5089,7 +5086,7 @@
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C41">
         <v>3.5749528668221631</v>
@@ -5101,13 +5098,13 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="U41" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V41" t="s">
         <v>400</v>
       </c>
       <c r="W41" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X41" t="s">
         <v>363</v>
@@ -5115,7 +5112,7 @@
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C42">
         <v>1.7874764334110815</v>
@@ -5127,13 +5124,13 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="U42" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V42" t="s">
         <v>401</v>
       </c>
       <c r="W42" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X42" t="s">
         <v>363</v>
@@ -5141,7 +5138,7 @@
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C43">
         <v>1.7874764334110815</v>
@@ -5153,7 +5150,7 @@
         <v>0.98841999999999997</v>
       </c>
       <c r="U43" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V43" t="s">
         <v>402</v>
@@ -5167,7 +5164,7 @@
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C44">
         <v>1.7874764334110815</v>
@@ -5179,7 +5176,7 @@
         <v>0.98817999999999995</v>
       </c>
       <c r="U44" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V44" t="s">
         <v>404</v>
@@ -5193,7 +5190,7 @@
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C45">
         <v>1.7874764334110815</v>
@@ -5205,7 +5202,7 @@
         <v>0.99519999999999997</v>
       </c>
       <c r="U45" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V45" t="s">
         <v>405</v>
@@ -5219,7 +5216,7 @@
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C46">
         <v>1.7874764334110815</v>
@@ -5231,7 +5228,7 @@
         <v>0.99963999999999997</v>
       </c>
       <c r="U46" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V46" t="s">
         <v>406</v>
@@ -5245,7 +5242,7 @@
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C47">
         <v>1.7874764334110815</v>
@@ -5257,7 +5254,7 @@
         <v>0.99514000000000002</v>
       </c>
       <c r="U47" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V47" t="s">
         <v>407</v>
@@ -5271,7 +5268,7 @@
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C48">
         <v>1.7874764334110815</v>
@@ -5283,7 +5280,7 @@
         <v>0.99328000000000005</v>
       </c>
       <c r="U48" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V48" t="s">
         <v>408</v>
@@ -5297,7 +5294,7 @@
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C49">
         <v>3.5749528668221631</v>
@@ -5309,7 +5306,7 @@
         <v>0.98241999999999996</v>
       </c>
       <c r="U49" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V49" t="s">
         <v>409</v>
@@ -5323,7 +5320,7 @@
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C50">
         <v>3.5749528668221631</v>
@@ -5335,7 +5332,7 @@
         <v>0.98331999999999997</v>
       </c>
       <c r="U50" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V50" t="s">
         <v>410</v>
@@ -5349,7 +5346,7 @@
     </row>
     <row r="51" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C51">
         <v>1.7874764334110815</v>
@@ -5361,7 +5358,7 @@
         <v>0.98187999999999998</v>
       </c>
       <c r="U51" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V51" t="s">
         <v>411</v>
@@ -5375,7 +5372,7 @@
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C52">
         <v>5.5120784900071946</v>
@@ -5387,7 +5384,7 @@
         <v>0.99970000000000003</v>
       </c>
       <c r="U52" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V52" t="s">
         <v>412</v>
@@ -5401,7 +5398,7 @@
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C53">
         <v>5.5120784900071946</v>
@@ -5413,7 +5410,7 @@
         <v>0.98194000000000004</v>
       </c>
       <c r="U53" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V53" t="s">
         <v>413</v>
@@ -5427,7 +5424,7 @@
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C54">
         <v>1.7874764334110815</v>
@@ -5439,7 +5436,7 @@
         <v>0.99207999999999996</v>
       </c>
       <c r="U54" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V54" t="s">
         <v>414</v>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C55">
         <v>1.7874764334110815</v>
@@ -5465,7 +5462,7 @@
         <v>0.98482000000000003</v>
       </c>
       <c r="U55" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V55" t="s">
         <v>415</v>
@@ -5479,7 +5476,7 @@
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C56">
         <v>1.7874764334110815</v>
@@ -5491,7 +5488,7 @@
         <v>0.99256</v>
       </c>
       <c r="U56" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V56" t="s">
         <v>416</v>
@@ -5505,7 +5502,7 @@
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C57">
         <v>5.5120784900071946</v>
@@ -5517,7 +5514,7 @@
         <v>0.98080000000000001</v>
       </c>
       <c r="U57" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V57" t="s">
         <v>418</v>
@@ -5531,7 +5528,7 @@
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C58">
         <v>1.7874764334110815</v>
@@ -5543,7 +5540,7 @@
         <v>0.98385999999999996</v>
       </c>
       <c r="U58" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V58" t="s">
         <v>419</v>
@@ -5557,7 +5554,7 @@
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C59">
         <v>1.7874764334110815</v>
@@ -5569,7 +5566,7 @@
         <v>0.96963999999999995</v>
       </c>
       <c r="U59" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V59" t="s">
         <v>420</v>
@@ -5583,7 +5580,7 @@
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C60">
         <v>1.7874764334110815</v>
@@ -5595,7 +5592,7 @@
         <v>0.96909999999999996</v>
       </c>
       <c r="U60" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V60" t="s">
         <v>421</v>
@@ -5609,7 +5606,7 @@
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C61">
         <v>1.7874764334110815</v>
@@ -5621,7 +5618,7 @@
         <v>0.99172000000000005</v>
       </c>
       <c r="U61" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V61" t="s">
         <v>422</v>
@@ -5635,7 +5632,7 @@
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C62">
         <v>1.7874764334110815</v>
@@ -5647,7 +5644,7 @@
         <v>0.98704000000000003</v>
       </c>
       <c r="U62" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V62" t="s">
         <v>423</v>
@@ -5661,7 +5658,7 @@
     </row>
     <row r="63" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C63">
         <v>3.5749528668221631</v>
@@ -5673,7 +5670,7 @@
         <v>0.99316000000000004</v>
       </c>
       <c r="U63" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V63" t="s">
         <v>424</v>
@@ -5687,7 +5684,7 @@
     </row>
     <row r="64" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C64">
         <v>3.5749528668221631</v>
@@ -5699,7 +5696,7 @@
         <v>0.99321999999999999</v>
       </c>
       <c r="U64" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V64" t="s">
         <v>425</v>
@@ -5713,7 +5710,7 @@
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C65">
         <v>1.7874764334110815</v>
@@ -5725,7 +5722,7 @@
         <v>0.99339999999999995</v>
       </c>
       <c r="U65" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V65" t="s">
         <v>426</v>
@@ -5739,7 +5736,7 @@
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C66">
         <v>1.7874764334110815</v>
@@ -5751,7 +5748,7 @@
         <v>0.99951999999999996</v>
       </c>
       <c r="U66" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V66" t="s">
         <v>427</v>
@@ -5765,7 +5762,7 @@
     </row>
     <row r="67" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C67">
         <v>1.7874764334110815</v>
@@ -5777,7 +5774,7 @@
         <v>0.99748000000000003</v>
       </c>
       <c r="U67" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V67" t="s">
         <v>428</v>
@@ -5791,7 +5788,7 @@
     </row>
     <row r="68" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C68">
         <v>3.5749528668221631</v>
@@ -5803,7 +5800,7 @@
         <v>0.99507999999999996</v>
       </c>
       <c r="U68" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V68" t="s">
         <v>429</v>
@@ -5817,7 +5814,7 @@
     </row>
     <row r="69" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C69">
         <v>1.7874764334110815</v>
@@ -5829,7 +5826,7 @@
         <v>0.99448000000000003</v>
       </c>
       <c r="U69" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V69" t="s">
         <v>430</v>
@@ -5843,7 +5840,7 @@
     </row>
     <row r="70" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C70">
         <v>3.5749528668221644</v>
@@ -5855,7 +5852,7 @@
         <v>0.99783999999999995</v>
       </c>
       <c r="U70" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V70" t="s">
         <v>432</v>
@@ -5869,7 +5866,7 @@
     </row>
     <row r="71" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C71">
         <v>1.7874764334110815</v>
@@ -5881,7 +5878,7 @@
         <v>0.99292000000000002</v>
       </c>
       <c r="U71" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V71" t="s">
         <v>433</v>
@@ -5895,7 +5892,7 @@
     </row>
     <row r="72" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C72">
         <v>1.7874764334110815</v>
@@ -5907,7 +5904,7 @@
         <v>0.99651999999999996</v>
       </c>
       <c r="U72" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V72" t="s">
         <v>434</v>
@@ -5921,7 +5918,7 @@
     </row>
     <row r="73" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C73">
         <v>1.7874764334110815</v>
@@ -5933,7 +5930,7 @@
         <v>0.98080000000000001</v>
       </c>
       <c r="U73" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V73" t="s">
         <v>435</v>
@@ -5947,7 +5944,7 @@
     </row>
     <row r="74" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C74">
         <v>1.7874764334110815</v>
@@ -5959,7 +5956,7 @@
         <v>0.99748000000000003</v>
       </c>
       <c r="U74" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V74" t="s">
         <v>436</v>
@@ -5973,7 +5970,7 @@
     </row>
     <row r="75" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C75">
         <v>3.5749528668221631</v>
@@ -5985,7 +5982,7 @@
         <v>0.99658000000000002</v>
       </c>
       <c r="U75" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V75" t="s">
         <v>437</v>
@@ -5999,7 +5996,7 @@
     </row>
     <row r="76" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C76">
         <v>1.7874764334110815</v>
@@ -6011,7 +6008,7 @@
         <v>0.99646000000000001</v>
       </c>
       <c r="U76" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V76" t="s">
         <v>438</v>
@@ -6025,7 +6022,7 @@
     </row>
     <row r="77" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C77">
         <v>1.7874764334110815</v>
@@ -6037,7 +6034,7 @@
         <v>0.99783999999999995</v>
       </c>
       <c r="U77" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V77" t="s">
         <v>439</v>
@@ -6051,7 +6048,7 @@
     </row>
     <row r="78" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C78">
         <v>3.5749528668221631</v>
@@ -6063,7 +6060,7 @@
         <v>0.99214000000000002</v>
       </c>
       <c r="U78" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V78" t="s">
         <v>440</v>
@@ -6077,7 +6074,7 @@
     </row>
     <row r="79" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C79">
         <v>1.7874764334110815</v>
@@ -6089,7 +6086,7 @@
         <v>0.99694000000000005</v>
       </c>
       <c r="U79" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V79" t="s">
         <v>441</v>
@@ -6103,7 +6100,7 @@
     </row>
     <row r="80" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C80">
         <v>1.7874764334110815</v>
@@ -6115,7 +6112,7 @@
         <v>0.99694000000000005</v>
       </c>
       <c r="U80" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V80" t="s">
         <v>442</v>
@@ -6129,7 +6126,7 @@
     </row>
     <row r="81" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C81">
         <v>3.5749528668221631</v>
@@ -6141,7 +6138,7 @@
         <v>0.99807999999999997</v>
       </c>
       <c r="U81" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V81" t="s">
         <v>443</v>
@@ -6155,7 +6152,7 @@
     </row>
     <row r="82" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C82">
         <v>1.7874764334110815</v>
@@ -6167,7 +6164,7 @@
         <v>0.99904000000000004</v>
       </c>
       <c r="U82" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V82" t="s">
         <v>444</v>
@@ -6181,7 +6178,7 @@
     </row>
     <row r="83" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C83">
         <v>1.7874764334110815</v>
@@ -6193,7 +6190,7 @@
         <v>0.99550000000000005</v>
       </c>
       <c r="U83" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V83" t="s">
         <v>446</v>
@@ -6207,7 +6204,7 @@
     </row>
     <row r="84" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C84">
         <v>1.7874764334110815</v>
@@ -6219,7 +6216,7 @@
         <v>0.99729999999999996</v>
       </c>
       <c r="U84" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V84" t="s">
         <v>447</v>
@@ -6233,7 +6230,7 @@
     </row>
     <row r="85" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C85">
         <v>1.7874764334110815</v>
@@ -6245,7 +6242,7 @@
         <v>0.97936000000000001</v>
       </c>
       <c r="U85" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V85" t="s">
         <v>448</v>
@@ -6259,7 +6256,7 @@
     </row>
     <row r="86" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C86">
         <v>5.362429300233245</v>
@@ -6271,7 +6268,7 @@
         <v>0.99904000000000004</v>
       </c>
       <c r="U86" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V86" t="s">
         <v>449</v>
@@ -6285,7 +6282,7 @@
     </row>
     <row r="87" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C87">
         <v>11.024156980014389</v>
@@ -6297,7 +6294,7 @@
         <v>0.96730000000000005</v>
       </c>
       <c r="U87" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V87" t="s">
         <v>450</v>
@@ -6311,7 +6308,7 @@
     </row>
     <row r="88" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C88">
         <v>3.5749528668221644</v>
@@ -6323,7 +6320,7 @@
         <v>0.99909999999999999</v>
       </c>
       <c r="U88" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V88" t="s">
         <v>451</v>
@@ -6337,7 +6334,7 @@
     </row>
     <row r="89" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C89">
         <v>1.7874764334110815</v>
@@ -6349,7 +6346,7 @@
         <v>0.98619999999999997</v>
       </c>
       <c r="U89" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V89" t="s">
         <v>452</v>
@@ -6363,7 +6360,7 @@
     </row>
     <row r="90" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C90">
         <v>1.7874764334110815</v>
@@ -6375,7 +6372,7 @@
         <v>0.98926000000000003</v>
       </c>
       <c r="U90" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V90" t="s">
         <v>453</v>
@@ -6389,7 +6386,7 @@
     </row>
     <row r="91" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C91">
         <v>1.7874764334110815</v>
@@ -6401,7 +6398,7 @@
         <v>0.98662000000000005</v>
       </c>
       <c r="U91" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V91" t="s">
         <v>454</v>
@@ -6415,7 +6412,7 @@
     </row>
     <row r="92" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C92">
         <v>1.7874764334110815</v>
@@ -6427,7 +6424,7 @@
         <v>0.99346000000000001</v>
       </c>
       <c r="U92" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V92" t="s">
         <v>455</v>
@@ -6441,7 +6438,7 @@
     </row>
     <row r="93" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C93">
         <v>3.5749528668221631</v>
@@ -6453,7 +6450,7 @@
         <v>0.99694000000000005</v>
       </c>
       <c r="U93" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V93" t="s">
         <v>456</v>
@@ -6467,7 +6464,7 @@
     </row>
     <row r="94" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C94">
         <v>1.7874764334110815</v>
@@ -6479,7 +6476,7 @@
         <v>0.99856</v>
       </c>
       <c r="U94" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V94" t="s">
         <v>457</v>
@@ -6493,7 +6490,7 @@
     </row>
     <row r="95" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C95">
         <v>1.7874764334110815</v>
@@ -6505,7 +6502,7 @@
         <v>0.98440000000000005</v>
       </c>
       <c r="U95" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V95" t="s">
         <v>458</v>
@@ -6519,7 +6516,7 @@
     </row>
     <row r="96" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C96">
         <v>1.7874764334110815</v>
@@ -6531,7 +6528,7 @@
         <v>0.99975999999999998</v>
       </c>
       <c r="U96" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V96" t="s">
         <v>460</v>
@@ -6545,7 +6542,7 @@
     </row>
     <row r="97" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C97">
         <v>1.7874764334110815</v>
@@ -6557,7 +6554,7 @@
         <v>0.99412</v>
       </c>
       <c r="U97" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V97" t="s">
         <v>461</v>
@@ -6571,7 +6568,7 @@
     </row>
     <row r="98" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C98">
         <v>3.5749528668221631</v>
@@ -6583,7 +6580,7 @@
         <v>0.99982000000000004</v>
       </c>
       <c r="U98" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V98" t="s">
         <v>462</v>
@@ -6597,7 +6594,7 @@
     </row>
     <row r="99" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C99">
         <v>1.7874764334110815</v>
@@ -6609,7 +6606,7 @@
         <v>0.99441999999999997</v>
       </c>
       <c r="U99" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V99" t="s">
         <v>463</v>
@@ -6623,7 +6620,7 @@
     </row>
     <row r="100" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100">
         <v>1.7874764334110815</v>
@@ -6635,7 +6632,7 @@
         <v>0.99250000000000005</v>
       </c>
       <c r="U100" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V100" t="s">
         <v>464</v>
@@ -6649,7 +6646,7 @@
     </row>
     <row r="101" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C101">
         <v>3.5749528668221631</v>
@@ -6661,7 +6658,7 @@
         <v>0.99838000000000005</v>
       </c>
       <c r="U101" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V101" t="s">
         <v>465</v>
@@ -6675,7 +6672,7 @@
     </row>
     <row r="102" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C102">
         <v>1.7874764334110815</v>
@@ -6687,7 +6684,7 @@
         <v>0.99861999999999995</v>
       </c>
       <c r="U102" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V102" t="s">
         <v>466</v>
@@ -6701,7 +6698,7 @@
     </row>
     <row r="103" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C103">
         <v>1.7874764334110815</v>
@@ -6713,7 +6710,7 @@
         <v>0.99141999999999997</v>
       </c>
       <c r="U103" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V103" t="s">
         <v>467</v>
@@ -6727,7 +6724,7 @@
     </row>
     <row r="104" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C104">
         <v>1.7874764334110815</v>
@@ -6739,7 +6736,7 @@
         <v>0.99663999999999997</v>
       </c>
       <c r="U104" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V104" t="s">
         <v>468</v>
@@ -6753,7 +6750,7 @@
     </row>
     <row r="105" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C105">
         <v>3.5749528668221631</v>
@@ -6765,7 +6762,7 @@
         <v>0.99609999999999999</v>
       </c>
       <c r="U105" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V105" t="s">
         <v>469</v>
@@ -6779,7 +6776,7 @@
     </row>
     <row r="106" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C106">
         <v>1.7874764334110815</v>
@@ -6791,7 +6788,7 @@
         <v>0.98451999999999995</v>
       </c>
       <c r="U106" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V106" t="s">
         <v>470</v>
@@ -6805,7 +6802,7 @@
     </row>
     <row r="107" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C107">
         <v>5.5120784900071946</v>
@@ -6817,7 +6814,7 @@
         <v>0.99195999999999995</v>
       </c>
       <c r="U107" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V107" t="s">
         <v>471</v>
@@ -6831,7 +6828,7 @@
     </row>
     <row r="108" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C108">
         <v>1.7874764334110815</v>
@@ -6843,7 +6840,7 @@
         <v>0.98884000000000005</v>
       </c>
       <c r="U108" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V108" t="s">
         <v>472</v>
@@ -6857,7 +6854,7 @@
     </row>
     <row r="109" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C109">
         <v>1.7874764334110815</v>
@@ -6869,7 +6866,7 @@
         <v>0.9829</v>
       </c>
       <c r="U109" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V109" t="s">
         <v>474</v>
@@ -6883,7 +6880,7 @@
     </row>
     <row r="110" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C110">
         <v>1.7874764334110815</v>
@@ -6895,7 +6892,7 @@
         <v>0.99826000000000004</v>
       </c>
       <c r="U110" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V110" t="s">
         <v>475</v>
@@ -6909,7 +6906,7 @@
     </row>
     <row r="111" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C111">
         <v>1.7874764334110815</v>
@@ -6921,7 +6918,7 @@
         <v>0.99850000000000005</v>
       </c>
       <c r="U111" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V111" t="s">
         <v>476</v>
@@ -6935,7 +6932,7 @@
     </row>
     <row r="112" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C112">
         <v>1.7874764334110815</v>
@@ -6947,7 +6944,7 @@
         <v>0.98548000000000002</v>
       </c>
       <c r="U112" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V112" t="s">
         <v>477</v>
@@ -6961,7 +6958,7 @@
     </row>
     <row r="113" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C113">
         <v>1.7874764334110815</v>
@@ -6973,7 +6970,7 @@
         <v>0.98775999999999997</v>
       </c>
       <c r="U113" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V113" t="s">
         <v>478</v>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="114" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C114">
         <v>5.362429300233245</v>
@@ -6999,7 +6996,7 @@
         <v>0.99958000000000002</v>
       </c>
       <c r="U114" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V114" t="s">
         <v>479</v>
@@ -7013,7 +7010,7 @@
     </row>
     <row r="115" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C115">
         <v>1.7874764334110815</v>
@@ -7025,7 +7022,7 @@
         <v>0.99658000000000002</v>
       </c>
       <c r="U115" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V115" t="s">
         <v>480</v>
@@ -7039,7 +7036,7 @@
     </row>
     <row r="116" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C116">
         <v>1.7874764334110815</v>
@@ -7051,7 +7048,7 @@
         <v>0.99394000000000005</v>
       </c>
       <c r="U116" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V116" t="s">
         <v>481</v>
@@ -7065,7 +7062,7 @@
     </row>
     <row r="117" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C117">
         <v>1.7874764334110815</v>
@@ -7077,7 +7074,7 @@
         <v>0.99790000000000001</v>
       </c>
       <c r="U117" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V117" t="s">
         <v>482</v>
@@ -7091,7 +7088,7 @@
     </row>
     <row r="118" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C118">
         <v>1.7874764334110815</v>
@@ -7103,7 +7100,7 @@
         <v>0.99399999999999999</v>
       </c>
       <c r="U118" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V118" t="s">
         <v>483</v>
@@ -7117,7 +7114,7 @@
     </row>
     <row r="119" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C119">
         <v>1.7874764334110815</v>
@@ -7129,7 +7126,7 @@
         <v>0.98914000000000002</v>
       </c>
       <c r="U119" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V119" t="s">
         <v>484</v>
@@ -7143,7 +7140,7 @@
     </row>
     <row r="120" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C120">
         <v>1.7874764334110815</v>
@@ -7155,7 +7152,7 @@
         <v>0.99184000000000005</v>
       </c>
       <c r="U120" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V120" t="s">
         <v>485</v>
@@ -7169,7 +7166,7 @@
     </row>
     <row r="121" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C121">
         <v>1.7874764334110815</v>
@@ -7181,7 +7178,7 @@
         <v>0.98692000000000002</v>
       </c>
       <c r="U121" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V121" t="s">
         <v>486</v>
@@ -7195,7 +7192,7 @@
     </row>
     <row r="122" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C122">
         <v>1.7874764334110815</v>
@@ -7207,7 +7204,7 @@
         <v>0.99765999999999999</v>
       </c>
       <c r="U122" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V122" t="s">
         <v>488</v>
@@ -7221,7 +7218,7 @@
     </row>
     <row r="123" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C123">
         <v>5.5120784900071946</v>
@@ -7233,7 +7230,7 @@
         <v>0.98728000000000005</v>
       </c>
       <c r="U123" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V123" t="s">
         <v>489</v>
@@ -7247,7 +7244,7 @@
     </row>
     <row r="124" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C124">
         <v>3.5749528668221631</v>
@@ -7259,7 +7256,7 @@
         <v>0.99285999999999996</v>
       </c>
       <c r="U124" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V124" t="s">
         <v>490</v>
@@ -7273,7 +7270,7 @@
     </row>
     <row r="125" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C125">
         <v>1.7874764334110815</v>
@@ -7285,7 +7282,7 @@
         <v>0.99214000000000002</v>
       </c>
       <c r="U125" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V125" t="s">
         <v>491</v>
@@ -7299,7 +7296,7 @@
     </row>
     <row r="126" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C126">
         <v>1.7874764334110815</v>
@@ -7311,7 +7308,7 @@
         <v>0.99136000000000002</v>
       </c>
       <c r="U126" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V126" t="s">
         <v>492</v>
@@ -7325,7 +7322,7 @@
     </row>
     <row r="127" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C127">
         <v>1.7874764334110815</v>
@@ -7337,7 +7334,7 @@
         <v>0.99568000000000001</v>
       </c>
       <c r="U127" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V127" t="s">
         <v>493</v>
@@ -7351,7 +7348,7 @@
     </row>
     <row r="128" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C128">
         <v>3.5749528668221631</v>
@@ -7363,7 +7360,7 @@
         <v>0.99129999999999996</v>
       </c>
       <c r="U128" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V128" t="s">
         <v>494</v>
@@ -7377,7 +7374,7 @@
     </row>
     <row r="129" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C129">
         <v>3.5749528668221631</v>
@@ -7389,7 +7386,7 @@
         <v>0.99339999999999995</v>
       </c>
       <c r="U129" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V129" t="s">
         <v>495</v>
@@ -7403,7 +7400,7 @@
     </row>
     <row r="130" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C130">
         <v>3.5749528668221631</v>
@@ -7415,7 +7412,7 @@
         <v>0.98895999999999995</v>
       </c>
       <c r="U130" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V130" t="s">
         <v>496</v>
@@ -7429,7 +7426,7 @@
     </row>
     <row r="131" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C131">
         <v>1.7874764334110815</v>
@@ -7441,7 +7438,7 @@
         <v>0.99021999999999999</v>
       </c>
       <c r="U131" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V131" t="s">
         <v>497</v>
@@ -7455,7 +7452,7 @@
     </row>
     <row r="132" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C132">
         <v>1.7874764334110815</v>
@@ -7467,7 +7464,7 @@
         <v>0.99375999999999998</v>
       </c>
       <c r="U132" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V132" t="s">
         <v>498</v>
@@ -7481,7 +7478,7 @@
     </row>
     <row r="133" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C133">
         <v>1.7874764334110815</v>
@@ -7493,7 +7490,7 @@
         <v>0.99339999999999995</v>
       </c>
       <c r="U133" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V133" t="s">
         <v>499</v>
@@ -7507,7 +7504,7 @@
     </row>
     <row r="134" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C134">
         <v>1.7874764334110815</v>
@@ -7519,7 +7516,7 @@
         <v>0.99177999999999999</v>
       </c>
       <c r="U134" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V134" t="s">
         <v>500</v>
@@ -7533,7 +7530,7 @@
     </row>
     <row r="135" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C135">
         <v>1.7874764334110815</v>
@@ -7545,7 +7542,7 @@
         <v>0.99880000000000002</v>
       </c>
       <c r="U135" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V135" t="s">
         <v>502</v>
@@ -7559,7 +7556,7 @@
     </row>
     <row r="136" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C136">
         <v>1.7874764334110815</v>
@@ -7571,7 +7568,7 @@
         <v>0.99963999999999997</v>
       </c>
       <c r="U136" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V136" t="s">
         <v>503</v>
@@ -7585,7 +7582,7 @@
     </row>
     <row r="137" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C137">
         <v>1.7874764334110815</v>
@@ -7597,7 +7594,7 @@
         <v>0.98326000000000002</v>
       </c>
       <c r="U137" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V137" t="s">
         <v>504</v>
@@ -7611,7 +7608,7 @@
     </row>
     <row r="138" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C138">
         <v>1.7874764334110815</v>
@@ -7623,7 +7620,7 @@
         <v>0.99814000000000003</v>
       </c>
       <c r="U138" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V138" t="s">
         <v>505</v>
@@ -7637,7 +7634,7 @@
     </row>
     <row r="139" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C139">
         <v>5.5120784900071946</v>
@@ -7649,7 +7646,7 @@
         <v>0.97155999999999998</v>
       </c>
       <c r="U139" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V139" t="s">
         <v>506</v>
@@ -7663,7 +7660,7 @@
     </row>
     <row r="140" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C140">
         <v>1.7874764334110815</v>
@@ -7675,7 +7672,7 @@
         <v>0.99346000000000001</v>
       </c>
       <c r="U140" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V140" t="s">
         <v>507</v>
@@ -7689,7 +7686,7 @@
     </row>
     <row r="141" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C141">
         <v>1.7874764334110815</v>
@@ -7701,7 +7698,7 @@
         <v>0.997</v>
       </c>
       <c r="U141" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V141" t="s">
         <v>508</v>
@@ -7715,7 +7712,7 @@
     </row>
     <row r="142" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C142">
         <v>3.5749528668221644</v>
@@ -7727,7 +7724,7 @@
         <v>0.99939999999999996</v>
       </c>
       <c r="U142" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V142" t="s">
         <v>509</v>
@@ -7741,7 +7738,7 @@
     </row>
     <row r="143" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C143">
         <v>1.7874764334110815</v>
@@ -7753,7 +7750,7 @@
         <v>0.98853999999999997</v>
       </c>
       <c r="U143" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V143" t="s">
         <v>510</v>
@@ -7767,7 +7764,7 @@
     </row>
     <row r="144" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B144" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C144">
         <v>1.7874764334110815</v>
@@ -7779,7 +7776,7 @@
         <v>0.99621999999999999</v>
       </c>
       <c r="U144" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V144" t="s">
         <v>511</v>
@@ -7793,7 +7790,7 @@
     </row>
     <row r="145" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B145" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C145">
         <v>1.7874764334110815</v>
@@ -7805,7 +7802,7 @@
         <v>0.99214000000000002</v>
       </c>
       <c r="U145" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V145" t="s">
         <v>512</v>
@@ -7819,7 +7816,7 @@
     </row>
     <row r="146" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C146">
         <v>1.7874764334110815</v>
@@ -7831,7 +7828,7 @@
         <v>0.99526000000000003</v>
       </c>
       <c r="U146" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V146" t="s">
         <v>513</v>
@@ -7845,7 +7842,7 @@
     </row>
     <row r="147" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C147">
         <v>1.7874764334110815</v>
@@ -7857,7 +7854,7 @@
         <v>0.98272000000000004</v>
       </c>
       <c r="U147" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V147" t="s">
         <v>514</v>
@@ -7871,7 +7868,7 @@
     </row>
     <row r="148" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C148">
         <v>1.7874764334110815</v>
@@ -7883,7 +7880,7 @@
         <v>0.99729999999999996</v>
       </c>
       <c r="U148" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V148" t="s">
         <v>516</v>
@@ -7897,7 +7894,7 @@
     </row>
     <row r="149" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C149">
         <v>1.7874764334110815</v>
@@ -7909,7 +7906,7 @@
         <v>0.997</v>
       </c>
       <c r="U149" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V149" t="s">
         <v>517</v>
@@ -7923,7 +7920,7 @@
     </row>
     <row r="150" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C150">
         <v>3.5749528668221631</v>
@@ -7935,7 +7932,7 @@
         <v>0.98931999999999998</v>
       </c>
       <c r="U150" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V150" t="s">
         <v>518</v>
@@ -7949,7 +7946,7 @@
     </row>
     <row r="151" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C151">
         <v>3.5749528668221631</v>
@@ -7961,7 +7958,7 @@
         <v>0.98607999999999996</v>
       </c>
       <c r="U151" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V151" t="s">
         <v>519</v>
@@ -7975,7 +7972,7 @@
     </row>
     <row r="152" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C152">
         <v>3.5749528668221631</v>
@@ -7987,7 +7984,7 @@
         <v>0.99753999999999998</v>
       </c>
       <c r="U152" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V152" t="s">
         <v>520</v>
@@ -8001,7 +7998,7 @@
     </row>
     <row r="153" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B153" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C153">
         <v>3.5749528668221631</v>
@@ -8013,7 +8010,7 @@
         <v>0.98956</v>
       </c>
       <c r="U153" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V153" t="s">
         <v>521</v>
@@ -8027,7 +8024,7 @@
     </row>
     <row r="154" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C154">
         <v>1.7874764334110815</v>
@@ -8039,7 +8036,7 @@
         <v>0.99328000000000005</v>
       </c>
       <c r="U154" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V154" t="s">
         <v>522</v>
@@ -8053,7 +8050,7 @@
     </row>
     <row r="155" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C155">
         <v>1.7874764334110815</v>
@@ -8065,7 +8062,7 @@
         <v>0.99309999999999998</v>
       </c>
       <c r="U155" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V155" t="s">
         <v>523</v>
@@ -8079,7 +8076,7 @@
     </row>
     <row r="156" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C156">
         <v>1.7874764334110815</v>
@@ -8091,7 +8088,7 @@
         <v>0.99856</v>
       </c>
       <c r="U156" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V156" t="s">
         <v>524</v>
@@ -8105,7 +8102,7 @@
     </row>
     <row r="157" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B157" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C157">
         <v>1.7874764334110815</v>
@@ -8117,7 +8114,7 @@
         <v>0.99838000000000005</v>
       </c>
       <c r="U157" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V157" t="s">
         <v>525</v>
@@ -8131,7 +8128,7 @@
     </row>
     <row r="158" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B158" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C158">
         <v>1.7874764334110815</v>
@@ -8143,7 +8140,7 @@
         <v>0.99885999999999997</v>
       </c>
       <c r="U158" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V158" t="s">
         <v>526</v>
@@ -8157,7 +8154,7 @@
     </row>
     <row r="159" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C159">
         <v>1.7874764334110815</v>
@@ -8169,7 +8166,7 @@
         <v>0.99195999999999995</v>
       </c>
       <c r="U159" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V159" t="s">
         <v>527</v>
@@ -8183,7 +8180,7 @@
     </row>
     <row r="160" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B160" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C160">
         <v>1.7874764334110815</v>
@@ -8195,7 +8192,7 @@
         <v>0.99328000000000005</v>
       </c>
       <c r="U160" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V160" t="s">
         <v>528</v>
@@ -8209,7 +8206,7 @@
     </row>
     <row r="161" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C161">
         <v>3.5749528668221631</v>
@@ -8221,7 +8218,7 @@
         <v>0.99358000000000002</v>
       </c>
       <c r="U161" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V161" t="s">
         <v>530</v>
@@ -8235,7 +8232,7 @@
     </row>
     <row r="162" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B162" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C162">
         <v>3.5749528668221631</v>
@@ -8247,7 +8244,7 @@
         <v>0.99939999999999996</v>
       </c>
       <c r="U162" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V162" t="s">
         <v>531</v>
@@ -8261,7 +8258,7 @@
     </row>
     <row r="163" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B163" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C163">
         <v>1.7874764334110815</v>
@@ -8273,7 +8270,7 @@
         <v>0.99987999999999999</v>
       </c>
       <c r="U163" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V163" t="s">
         <v>532</v>
@@ -8287,7 +8284,7 @@
     </row>
     <row r="164" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C164">
         <v>1.7874764334110815</v>
@@ -8299,7 +8296,7 @@
         <v>0.99916000000000005</v>
       </c>
       <c r="U164" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V164" t="s">
         <v>533</v>
@@ -8313,7 +8310,7 @@
     </row>
     <row r="165" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C165">
         <v>1.7874764334110815</v>
@@ -8325,7 +8322,7 @@
         <v>0.99843999999999999</v>
       </c>
       <c r="U165" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V165" t="s">
         <v>534</v>
@@ -8339,7 +8336,7 @@
     </row>
     <row r="166" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B166" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C166">
         <v>1.7874764334110815</v>
@@ -8351,7 +8348,7 @@
         <v>0.99904000000000004</v>
       </c>
       <c r="U166" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V166" t="s">
         <v>535</v>
@@ -8365,7 +8362,7 @@
     </row>
     <row r="167" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B167" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C167">
         <v>1.7874764334110815</v>
@@ -8377,7 +8374,7 @@
         <v>0.98050000000000004</v>
       </c>
       <c r="U167" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V167" t="s">
         <v>536</v>
@@ -8391,7 +8388,7 @@
     </row>
     <row r="168" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C168">
         <v>1.7874764334110815</v>
@@ -8403,7 +8400,7 @@
         <v>0.99472000000000005</v>
       </c>
       <c r="U168" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V168" t="s">
         <v>537</v>
@@ -8417,7 +8414,7 @@
     </row>
     <row r="169" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C169">
         <v>1.7874764334110815</v>
@@ -8429,7 +8426,7 @@
         <v>0.99436000000000002</v>
       </c>
       <c r="U169" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V169" t="s">
         <v>538</v>
@@ -8443,7 +8440,7 @@
     </row>
     <row r="170" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C170">
         <v>1.7874764334110815</v>
@@ -8455,7 +8452,7 @@
         <v>0.99873999999999996</v>
       </c>
       <c r="U170" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V170" t="s">
         <v>539</v>
@@ -8469,7 +8466,7 @@
     </row>
     <row r="171" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C171">
         <v>1.7874764334110815</v>
@@ -8481,7 +8478,7 @@
         <v>0.99892000000000003</v>
       </c>
       <c r="U171" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V171" t="s">
         <v>540</v>
@@ -8495,7 +8492,7 @@
     </row>
     <row r="172" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C172">
         <v>3.5749528668221631</v>
@@ -8507,7 +8504,7 @@
         <v>0.99214000000000002</v>
       </c>
       <c r="U172" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V172" t="s">
         <v>541</v>
@@ -8521,7 +8518,7 @@
     </row>
     <row r="173" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C173">
         <v>1.7874764334110815</v>
@@ -8533,7 +8530,7 @@
         <v>0.99177999999999999</v>
       </c>
       <c r="U173" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V173" t="s">
         <v>542</v>
@@ -8547,7 +8544,7 @@
     </row>
     <row r="174" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C174">
         <v>1.7874764334110815</v>
@@ -8559,7 +8556,7 @@
         <v>0.98997999999999997</v>
       </c>
       <c r="U174" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V174" t="s">
         <v>544</v>
@@ -8573,7 +8570,7 @@
     </row>
     <row r="175" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B175" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C175">
         <v>3.5749528668221631</v>
@@ -8585,7 +8582,7 @@
         <v>0.99958000000000002</v>
       </c>
       <c r="U175" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V175" t="s">
         <v>545</v>
@@ -8599,7 +8596,7 @@
     </row>
     <row r="176" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B176" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C176">
         <v>3.5749528668221631</v>
@@ -8611,7 +8608,7 @@
         <v>0.99370000000000003</v>
       </c>
       <c r="U176" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V176" t="s">
         <v>546</v>
@@ -8625,7 +8622,7 @@
     </row>
     <row r="177" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C177">
         <v>1.7874764334110815</v>
@@ -8637,7 +8634,7 @@
         <v>0.99075999999999997</v>
       </c>
       <c r="U177" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V177" t="s">
         <v>547</v>
@@ -8651,7 +8648,7 @@
     </row>
     <row r="178" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C178">
         <v>1.7874764334110815</v>
@@ -8663,7 +8660,7 @@
         <v>0.98806000000000005</v>
       </c>
       <c r="U178" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V178" t="s">
         <v>548</v>
@@ -8677,7 +8674,7 @@
     </row>
     <row r="179" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B179" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C179">
         <v>1.7874764334110815</v>
@@ -8689,7 +8686,7 @@
         <v>0.97419999999999995</v>
       </c>
       <c r="U179" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V179" t="s">
         <v>549</v>
@@ -8703,7 +8700,7 @@
     </row>
     <row r="180" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B180" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C180">
         <v>11.024156980014389</v>
@@ -8715,7 +8712,7 @@
         <v>0.99922</v>
       </c>
       <c r="U180" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V180" t="s">
         <v>550</v>
@@ -8729,7 +8726,7 @@
     </row>
     <row r="181" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C181">
         <v>5.5120784900071946</v>
@@ -8741,7 +8738,7 @@
         <v>0.98560000000000003</v>
       </c>
       <c r="U181" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V181" t="s">
         <v>551</v>
@@ -8755,7 +8752,7 @@
     </row>
     <row r="182" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C182">
         <v>5.5120784900071946</v>
@@ -8767,7 +8764,7 @@
         <v>0.97287999999999997</v>
       </c>
       <c r="U182" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V182" t="s">
         <v>552</v>
@@ -8781,7 +8778,7 @@
     </row>
     <row r="183" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C183">
         <v>1.7874764334110815</v>
@@ -8793,7 +8790,7 @@
         <v>0.98746</v>
       </c>
       <c r="U183" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V183" t="s">
         <v>553</v>
@@ -8807,7 +8804,7 @@
     </row>
     <row r="184" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B184" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C184">
         <v>3.5749528668221631</v>
@@ -8819,7 +8816,7 @@
         <v>0.99934000000000001</v>
       </c>
       <c r="U184" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V184" t="s">
         <v>554</v>
@@ -8833,7 +8830,7 @@
     </row>
     <row r="185" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C185">
         <v>3.5749528668221631</v>
@@ -8845,7 +8842,7 @@
         <v>0.99526000000000003</v>
       </c>
       <c r="U185" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V185" t="s">
         <v>555</v>
@@ -8859,7 +8856,7 @@
     </row>
     <row r="186" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U186" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V186" t="s">
         <v>556</v>
@@ -8873,7 +8870,7 @@
     </row>
     <row r="187" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U187" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V187" t="s">
         <v>558</v>
@@ -8887,7 +8884,7 @@
     </row>
     <row r="188" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U188" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V188" t="s">
         <v>559</v>
@@ -8901,7 +8898,7 @@
     </row>
     <row r="189" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U189" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V189" t="s">
         <v>560</v>
@@ -8915,7 +8912,7 @@
     </row>
     <row r="190" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U190" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V190" t="s">
         <v>561</v>
@@ -8929,7 +8926,7 @@
     </row>
     <row r="191" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U191" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V191" t="s">
         <v>562</v>
@@ -8943,7 +8940,7 @@
     </row>
     <row r="192" spans="2:24" x14ac:dyDescent="0.45">
       <c r="U192" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V192" t="s">
         <v>563</v>
@@ -8957,7 +8954,7 @@
     </row>
     <row r="193" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U193" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V193" t="s">
         <v>564</v>
@@ -8971,7 +8968,7 @@
     </row>
     <row r="194" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U194" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V194" t="s">
         <v>565</v>
@@ -8985,7 +8982,7 @@
     </row>
     <row r="195" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U195" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V195" t="s">
         <v>566</v>
@@ -8999,7 +8996,7 @@
     </row>
     <row r="196" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U196" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V196" t="s">
         <v>567</v>
@@ -9013,7 +9010,7 @@
     </row>
     <row r="197" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U197" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V197" t="s">
         <v>568</v>
@@ -9027,7 +9024,7 @@
     </row>
     <row r="198" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U198" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V198" t="s">
         <v>569</v>
@@ -9041,7 +9038,7 @@
     </row>
     <row r="199" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U199" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V199" t="s">
         <v>570</v>
@@ -9055,7 +9052,7 @@
     </row>
     <row r="200" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U200" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V200" t="s">
         <v>572</v>
@@ -9069,7 +9066,7 @@
     </row>
     <row r="201" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U201" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V201" t="s">
         <v>573</v>
@@ -9083,7 +9080,7 @@
     </row>
     <row r="202" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U202" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V202" t="s">
         <v>574</v>
@@ -9097,7 +9094,7 @@
     </row>
     <row r="203" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U203" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V203" t="s">
         <v>575</v>
@@ -9111,7 +9108,7 @@
     </row>
     <row r="204" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U204" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V204" t="s">
         <v>576</v>
@@ -9125,7 +9122,7 @@
     </row>
     <row r="205" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U205" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V205" t="s">
         <v>577</v>
@@ -9139,7 +9136,7 @@
     </row>
     <row r="206" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U206" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V206" t="s">
         <v>578</v>
@@ -9153,7 +9150,7 @@
     </row>
     <row r="207" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U207" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V207" t="s">
         <v>579</v>
@@ -9167,7 +9164,7 @@
     </row>
     <row r="208" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U208" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V208" t="s">
         <v>580</v>
@@ -9181,7 +9178,7 @@
     </row>
     <row r="209" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U209" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V209" t="s">
         <v>581</v>
@@ -9195,7 +9192,7 @@
     </row>
     <row r="210" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U210" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V210" t="s">
         <v>582</v>
@@ -9209,7 +9206,7 @@
     </row>
     <row r="211" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U211" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V211" t="s">
         <v>583</v>
@@ -9223,7 +9220,7 @@
     </row>
     <row r="212" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U212" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V212" t="s">
         <v>584</v>
@@ -9237,7 +9234,7 @@
     </row>
     <row r="213" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U213" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V213" t="s">
         <v>586</v>
@@ -9251,7 +9248,7 @@
     </row>
     <row r="214" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U214" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V214" t="s">
         <v>587</v>
@@ -9265,7 +9262,7 @@
     </row>
     <row r="215" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U215" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V215" t="s">
         <v>588</v>
@@ -9279,7 +9276,7 @@
     </row>
     <row r="216" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U216" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V216" t="s">
         <v>589</v>
@@ -9293,7 +9290,7 @@
     </row>
     <row r="217" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U217" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V217" t="s">
         <v>590</v>
@@ -9307,7 +9304,7 @@
     </row>
     <row r="218" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U218" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V218" t="s">
         <v>591</v>
@@ -9321,7 +9318,7 @@
     </row>
     <row r="219" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U219" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V219" t="s">
         <v>592</v>
@@ -9335,7 +9332,7 @@
     </row>
     <row r="220" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U220" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V220" t="s">
         <v>593</v>
@@ -9349,7 +9346,7 @@
     </row>
     <row r="221" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U221" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V221" t="s">
         <v>594</v>
@@ -9363,7 +9360,7 @@
     </row>
     <row r="222" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U222" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V222" t="s">
         <v>595</v>
@@ -9377,7 +9374,7 @@
     </row>
     <row r="223" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U223" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V223" t="s">
         <v>596</v>
@@ -9391,7 +9388,7 @@
     </row>
     <row r="224" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U224" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V224" t="s">
         <v>597</v>
@@ -9405,7 +9402,7 @@
     </row>
     <row r="225" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U225" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V225" t="s">
         <v>598</v>
@@ -9419,7 +9416,7 @@
     </row>
     <row r="226" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U226" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V226" t="s">
         <v>600</v>
@@ -9433,7 +9430,7 @@
     </row>
     <row r="227" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U227" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V227" t="s">
         <v>601</v>
@@ -9447,7 +9444,7 @@
     </row>
     <row r="228" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U228" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V228" t="s">
         <v>602</v>
@@ -9461,7 +9458,7 @@
     </row>
     <row r="229" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U229" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V229" t="s">
         <v>603</v>
@@ -9475,7 +9472,7 @@
     </row>
     <row r="230" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U230" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V230" t="s">
         <v>604</v>
@@ -9489,7 +9486,7 @@
     </row>
     <row r="231" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U231" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V231" t="s">
         <v>605</v>
@@ -9503,7 +9500,7 @@
     </row>
     <row r="232" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U232" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V232" t="s">
         <v>606</v>
@@ -9517,7 +9514,7 @@
     </row>
     <row r="233" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U233" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V233" t="s">
         <v>607</v>
@@ -9531,7 +9528,7 @@
     </row>
     <row r="234" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U234" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V234" t="s">
         <v>608</v>
@@ -9545,7 +9542,7 @@
     </row>
     <row r="235" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U235" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V235" t="s">
         <v>609</v>
@@ -9559,7 +9556,7 @@
     </row>
     <row r="236" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U236" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V236" t="s">
         <v>610</v>
@@ -9573,7 +9570,7 @@
     </row>
     <row r="237" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U237" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V237" t="s">
         <v>611</v>
@@ -9587,7 +9584,7 @@
     </row>
     <row r="238" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U238" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V238" t="s">
         <v>612</v>
@@ -9601,7 +9598,7 @@
     </row>
     <row r="239" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U239" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V239" t="s">
         <v>614</v>
@@ -9615,7 +9612,7 @@
     </row>
     <row r="240" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U240" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V240" t="s">
         <v>615</v>
@@ -9629,7 +9626,7 @@
     </row>
     <row r="241" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U241" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V241" t="s">
         <v>616</v>
@@ -9643,7 +9640,7 @@
     </row>
     <row r="242" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U242" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V242" t="s">
         <v>617</v>
@@ -9657,7 +9654,7 @@
     </row>
     <row r="243" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U243" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V243" t="s">
         <v>618</v>
@@ -9671,7 +9668,7 @@
     </row>
     <row r="244" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U244" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V244" t="s">
         <v>619</v>
@@ -9685,7 +9682,7 @@
     </row>
     <row r="245" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U245" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V245" t="s">
         <v>620</v>
@@ -9699,7 +9696,7 @@
     </row>
     <row r="246" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U246" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V246" t="s">
         <v>621</v>
@@ -9713,7 +9710,7 @@
     </row>
     <row r="247" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U247" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V247" t="s">
         <v>622</v>
@@ -9727,7 +9724,7 @@
     </row>
     <row r="248" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U248" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V248" t="s">
         <v>623</v>
@@ -9741,7 +9738,7 @@
     </row>
     <row r="249" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U249" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V249" t="s">
         <v>624</v>
@@ -9755,7 +9752,7 @@
     </row>
     <row r="250" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U250" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V250" t="s">
         <v>625</v>
@@ -9769,7 +9766,7 @@
     </row>
     <row r="251" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U251" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V251" t="s">
         <v>626</v>
@@ -9783,7 +9780,7 @@
     </row>
     <row r="252" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U252" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V252" t="s">
         <v>628</v>
@@ -9797,7 +9794,7 @@
     </row>
     <row r="253" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U253" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V253" t="s">
         <v>629</v>
@@ -9811,7 +9808,7 @@
     </row>
     <row r="254" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U254" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V254" t="s">
         <v>630</v>
@@ -9825,7 +9822,7 @@
     </row>
     <row r="255" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U255" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V255" t="s">
         <v>631</v>
@@ -9839,7 +9836,7 @@
     </row>
     <row r="256" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U256" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V256" t="s">
         <v>632</v>
@@ -9853,7 +9850,7 @@
     </row>
     <row r="257" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U257" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V257" t="s">
         <v>633</v>
@@ -9867,7 +9864,7 @@
     </row>
     <row r="258" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U258" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V258" t="s">
         <v>634</v>
@@ -9881,7 +9878,7 @@
     </row>
     <row r="259" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U259" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V259" t="s">
         <v>635</v>
@@ -9895,7 +9892,7 @@
     </row>
     <row r="260" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U260" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V260" t="s">
         <v>636</v>
@@ -9909,7 +9906,7 @@
     </row>
     <row r="261" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U261" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V261" t="s">
         <v>637</v>
@@ -9923,7 +9920,7 @@
     </row>
     <row r="262" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U262" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V262" t="s">
         <v>638</v>
@@ -9937,7 +9934,7 @@
     </row>
     <row r="263" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U263" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V263" t="s">
         <v>639</v>
@@ -9951,7 +9948,7 @@
     </row>
     <row r="264" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U264" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V264" t="s">
         <v>640</v>
@@ -9965,7 +9962,7 @@
     </row>
     <row r="265" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U265" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V265" t="s">
         <v>642</v>
@@ -9979,7 +9976,7 @@
     </row>
     <row r="266" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U266" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V266" t="s">
         <v>643</v>
@@ -9993,7 +9990,7 @@
     </row>
     <row r="267" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U267" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V267" t="s">
         <v>644</v>
@@ -10007,7 +10004,7 @@
     </row>
     <row r="268" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U268" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V268" t="s">
         <v>645</v>
@@ -10021,7 +10018,7 @@
     </row>
     <row r="269" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U269" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V269" t="s">
         <v>646</v>
@@ -10035,7 +10032,7 @@
     </row>
     <row r="270" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U270" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V270" t="s">
         <v>647</v>
@@ -10049,7 +10046,7 @@
     </row>
     <row r="271" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U271" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V271" t="s">
         <v>648</v>
@@ -10063,7 +10060,7 @@
     </row>
     <row r="272" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U272" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V272" t="s">
         <v>649</v>
@@ -10077,7 +10074,7 @@
     </row>
     <row r="273" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U273" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V273" t="s">
         <v>650</v>
@@ -10091,7 +10088,7 @@
     </row>
     <row r="274" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U274" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V274" t="s">
         <v>651</v>
@@ -10105,7 +10102,7 @@
     </row>
     <row r="275" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U275" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V275" t="s">
         <v>652</v>
@@ -10119,7 +10116,7 @@
     </row>
     <row r="276" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U276" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V276" t="s">
         <v>653</v>
@@ -10133,7 +10130,7 @@
     </row>
     <row r="277" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U277" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V277" t="s">
         <v>654</v>
@@ -10147,7 +10144,7 @@
     </row>
     <row r="278" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U278" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V278" t="s">
         <v>656</v>
@@ -10161,7 +10158,7 @@
     </row>
     <row r="279" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U279" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V279" t="s">
         <v>657</v>
@@ -10175,7 +10172,7 @@
     </row>
     <row r="280" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U280" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V280" t="s">
         <v>658</v>
@@ -10189,7 +10186,7 @@
     </row>
     <row r="281" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U281" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V281" t="s">
         <v>659</v>
@@ -10203,7 +10200,7 @@
     </row>
     <row r="282" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U282" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V282" t="s">
         <v>660</v>
@@ -10217,7 +10214,7 @@
     </row>
     <row r="283" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U283" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V283" t="s">
         <v>661</v>
@@ -10231,7 +10228,7 @@
     </row>
     <row r="284" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U284" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V284" t="s">
         <v>662</v>
@@ -10245,7 +10242,7 @@
     </row>
     <row r="285" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U285" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V285" t="s">
         <v>663</v>
@@ -10259,7 +10256,7 @@
     </row>
     <row r="286" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U286" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V286" t="s">
         <v>664</v>
@@ -10273,7 +10270,7 @@
     </row>
     <row r="287" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U287" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V287" t="s">
         <v>665</v>
@@ -10287,7 +10284,7 @@
     </row>
     <row r="288" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U288" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V288" t="s">
         <v>666</v>
@@ -10301,7 +10298,7 @@
     </row>
     <row r="289" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U289" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V289" t="s">
         <v>667</v>
@@ -10315,7 +10312,7 @@
     </row>
     <row r="290" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U290" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V290" t="s">
         <v>668</v>
@@ -10329,7 +10326,7 @@
     </row>
     <row r="291" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U291" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V291" t="s">
         <v>670</v>
@@ -10343,7 +10340,7 @@
     </row>
     <row r="292" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U292" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V292" t="s">
         <v>671</v>
@@ -10357,7 +10354,7 @@
     </row>
     <row r="293" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U293" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V293" t="s">
         <v>672</v>
@@ -10371,7 +10368,7 @@
     </row>
     <row r="294" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U294" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V294" t="s">
         <v>673</v>
@@ -10385,7 +10382,7 @@
     </row>
     <row r="295" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U295" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V295" t="s">
         <v>674</v>
@@ -10399,7 +10396,7 @@
     </row>
     <row r="296" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U296" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V296" t="s">
         <v>675</v>
@@ -10413,7 +10410,7 @@
     </row>
     <row r="297" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U297" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V297" t="s">
         <v>676</v>
@@ -10427,7 +10424,7 @@
     </row>
     <row r="298" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U298" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V298" t="s">
         <v>677</v>
@@ -10441,7 +10438,7 @@
     </row>
     <row r="299" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U299" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V299" t="s">
         <v>678</v>
@@ -10455,7 +10452,7 @@
     </row>
     <row r="300" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U300" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V300" t="s">
         <v>679</v>
@@ -10469,7 +10466,7 @@
     </row>
     <row r="301" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U301" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V301" t="s">
         <v>680</v>
@@ -10483,7 +10480,7 @@
     </row>
     <row r="302" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U302" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V302" t="s">
         <v>681</v>
@@ -10497,7 +10494,7 @@
     </row>
     <row r="303" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U303" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V303" t="s">
         <v>682</v>
@@ -10511,7 +10508,7 @@
     </row>
     <row r="304" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U304" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V304" t="s">
         <v>684</v>
@@ -10525,7 +10522,7 @@
     </row>
     <row r="305" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U305" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V305" t="s">
         <v>685</v>
@@ -10539,7 +10536,7 @@
     </row>
     <row r="306" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U306" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V306" t="s">
         <v>686</v>
@@ -10553,7 +10550,7 @@
     </row>
     <row r="307" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U307" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V307" t="s">
         <v>687</v>
@@ -10567,7 +10564,7 @@
     </row>
     <row r="308" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U308" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V308" t="s">
         <v>688</v>
@@ -10581,7 +10578,7 @@
     </row>
     <row r="309" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U309" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V309" t="s">
         <v>689</v>
@@ -10595,7 +10592,7 @@
     </row>
     <row r="310" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U310" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V310" t="s">
         <v>690</v>
@@ -10609,7 +10606,7 @@
     </row>
     <row r="311" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U311" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V311" t="s">
         <v>691</v>
@@ -10623,7 +10620,7 @@
     </row>
     <row r="312" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U312" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V312" t="s">
         <v>692</v>
@@ -10637,7 +10634,7 @@
     </row>
     <row r="313" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U313" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V313" t="s">
         <v>693</v>
@@ -10651,7 +10648,7 @@
     </row>
     <row r="314" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U314" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V314" t="s">
         <v>694</v>
@@ -10665,7 +10662,7 @@
     </row>
     <row r="315" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U315" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V315" t="s">
         <v>695</v>
@@ -10679,7 +10676,7 @@
     </row>
     <row r="316" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U316" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V316" t="s">
         <v>696</v>
@@ -10693,7 +10690,7 @@
     </row>
     <row r="317" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U317" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V317" t="s">
         <v>698</v>
@@ -10707,7 +10704,7 @@
     </row>
     <row r="318" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U318" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V318" t="s">
         <v>699</v>
@@ -10721,7 +10718,7 @@
     </row>
     <row r="319" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U319" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V319" t="s">
         <v>700</v>
@@ -10735,7 +10732,7 @@
     </row>
     <row r="320" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U320" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V320" t="s">
         <v>701</v>
@@ -10749,7 +10746,7 @@
     </row>
     <row r="321" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U321" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V321" t="s">
         <v>702</v>
@@ -10763,7 +10760,7 @@
     </row>
     <row r="322" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U322" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V322" t="s">
         <v>703</v>
@@ -10777,7 +10774,7 @@
     </row>
     <row r="323" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U323" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V323" t="s">
         <v>704</v>
@@ -10791,7 +10788,7 @@
     </row>
     <row r="324" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U324" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V324" t="s">
         <v>705</v>
@@ -10805,7 +10802,7 @@
     </row>
     <row r="325" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U325" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V325" t="s">
         <v>706</v>
@@ -10819,7 +10816,7 @@
     </row>
     <row r="326" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U326" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V326" t="s">
         <v>707</v>
@@ -10833,7 +10830,7 @@
     </row>
     <row r="327" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U327" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V327" t="s">
         <v>708</v>
@@ -10847,7 +10844,7 @@
     </row>
     <row r="328" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U328" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V328" t="s">
         <v>709</v>
@@ -10861,7 +10858,7 @@
     </row>
     <row r="329" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U329" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V329" t="s">
         <v>710</v>
@@ -10875,7 +10872,7 @@
     </row>
     <row r="330" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U330" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V330" t="s">
         <v>712</v>
@@ -10889,7 +10886,7 @@
     </row>
     <row r="331" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U331" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V331" t="s">
         <v>713</v>
@@ -10903,7 +10900,7 @@
     </row>
     <row r="332" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U332" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V332" t="s">
         <v>714</v>
@@ -10917,7 +10914,7 @@
     </row>
     <row r="333" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U333" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V333" t="s">
         <v>715</v>
@@ -10931,7 +10928,7 @@
     </row>
     <row r="334" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U334" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V334" t="s">
         <v>716</v>
@@ -10945,7 +10942,7 @@
     </row>
     <row r="335" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U335" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V335" t="s">
         <v>717</v>
@@ -10959,7 +10956,7 @@
     </row>
     <row r="336" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U336" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V336" t="s">
         <v>718</v>
@@ -10973,7 +10970,7 @@
     </row>
     <row r="337" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U337" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V337" t="s">
         <v>719</v>
@@ -10987,7 +10984,7 @@
     </row>
     <row r="338" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U338" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V338" t="s">
         <v>720</v>
@@ -11001,7 +10998,7 @@
     </row>
     <row r="339" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U339" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V339" t="s">
         <v>721</v>
@@ -11015,7 +11012,7 @@
     </row>
     <row r="340" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U340" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V340" t="s">
         <v>722</v>
@@ -11029,7 +11026,7 @@
     </row>
     <row r="341" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U341" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V341" t="s">
         <v>723</v>
@@ -11043,7 +11040,7 @@
     </row>
     <row r="342" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U342" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V342" t="s">
         <v>724</v>
@@ -11057,7 +11054,7 @@
     </row>
     <row r="343" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U343" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V343" t="s">
         <v>726</v>
@@ -11071,7 +11068,7 @@
     </row>
     <row r="344" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U344" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V344" t="s">
         <v>727</v>
@@ -11085,7 +11082,7 @@
     </row>
     <row r="345" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U345" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V345" t="s">
         <v>728</v>
@@ -11099,7 +11096,7 @@
     </row>
     <row r="346" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U346" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V346" t="s">
         <v>730</v>
@@ -11113,7 +11110,7 @@
     </row>
     <row r="347" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U347" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V347" t="s">
         <v>731</v>
@@ -11127,7 +11124,7 @@
     </row>
     <row r="348" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U348" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V348" t="s">
         <v>732</v>
@@ -11141,7 +11138,7 @@
     </row>
     <row r="349" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U349" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V349" t="s">
         <v>734</v>
@@ -11155,7 +11152,7 @@
     </row>
     <row r="350" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U350" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V350" t="s">
         <v>735</v>
@@ -11169,7 +11166,7 @@
     </row>
     <row r="351" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U351" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V351" t="s">
         <v>736</v>
@@ -11183,7 +11180,7 @@
     </row>
     <row r="352" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U352" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V352" t="s">
         <v>738</v>
@@ -11197,7 +11194,7 @@
     </row>
     <row r="353" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U353" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V353" t="s">
         <v>739</v>
@@ -11211,7 +11208,7 @@
     </row>
     <row r="354" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U354" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V354" t="s">
         <v>740</v>
@@ -11225,7 +11222,7 @@
     </row>
     <row r="355" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U355" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V355" t="s">
         <v>742</v>
@@ -11239,7 +11236,7 @@
     </row>
     <row r="356" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U356" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V356" t="s">
         <v>743</v>
@@ -11253,7 +11250,7 @@
     </row>
     <row r="357" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U357" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V357" t="s">
         <v>744</v>
@@ -11267,7 +11264,7 @@
     </row>
     <row r="358" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U358" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V358" t="s">
         <v>746</v>
@@ -11281,7 +11278,7 @@
     </row>
     <row r="359" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U359" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V359" t="s">
         <v>747</v>
@@ -11295,7 +11292,7 @@
     </row>
     <row r="360" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U360" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V360" t="s">
         <v>748</v>
@@ -11309,7 +11306,7 @@
     </row>
     <row r="361" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U361" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V361" t="s">
         <v>749</v>
@@ -11323,13 +11320,13 @@
     </row>
     <row r="362" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U362" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V362" t="s">
         <v>750</v>
       </c>
       <c r="W362" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X362" t="s">
         <v>363</v>
@@ -11337,13 +11334,13 @@
     </row>
     <row r="363" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U363" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V363" t="s">
         <v>751</v>
       </c>
       <c r="W363" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X363" t="s">
         <v>363</v>
@@ -11351,7 +11348,7 @@
     </row>
     <row r="364" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U364" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V364" t="s">
         <v>752</v>
@@ -11365,7 +11362,7 @@
     </row>
     <row r="365" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U365" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V365" t="s">
         <v>754</v>
@@ -11379,13 +11376,13 @@
     </row>
     <row r="366" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U366" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V366" t="s">
         <v>755</v>
       </c>
       <c r="W366" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X366" t="s">
         <v>363</v>
@@ -11393,13 +11390,13 @@
     </row>
     <row r="367" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U367" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V367" t="s">
         <v>756</v>
       </c>
       <c r="W367" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X367" t="s">
         <v>363</v>
@@ -11407,13 +11404,13 @@
     </row>
     <row r="368" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U368" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V368" t="s">
         <v>757</v>
       </c>
       <c r="W368" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X368" t="s">
         <v>363</v>
@@ -11421,13 +11418,13 @@
     </row>
     <row r="369" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U369" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V369" t="s">
         <v>758</v>
       </c>
       <c r="W369" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X369" t="s">
         <v>363</v>
@@ -11435,13 +11432,13 @@
     </row>
     <row r="370" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U370" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V370" t="s">
         <v>759</v>
       </c>
       <c r="W370" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X370" t="s">
         <v>363</v>
@@ -11449,13 +11446,13 @@
     </row>
     <row r="371" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U371" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V371" t="s">
         <v>760</v>
       </c>
       <c r="W371" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="X371" t="s">
         <v>363</v>
@@ -11463,7 +11460,7 @@
     </row>
     <row r="372" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U372" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V372" t="s">
         <v>761</v>
@@ -11477,7 +11474,7 @@
     </row>
     <row r="373" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U373" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V373" t="s">
         <v>762</v>
@@ -11491,7 +11488,7 @@
     </row>
     <row r="374" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U374" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V374" t="s">
         <v>763</v>
@@ -11505,7 +11502,7 @@
     </row>
     <row r="375" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U375" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V375" t="s">
         <v>764</v>
@@ -11519,7 +11516,7 @@
     </row>
     <row r="376" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U376" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V376" t="s">
         <v>765</v>
@@ -11533,7 +11530,7 @@
     </row>
     <row r="377" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U377" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V377" t="s">
         <v>766</v>
@@ -11547,7 +11544,7 @@
     </row>
     <row r="378" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U378" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V378" t="s">
         <v>767</v>
@@ -11561,7 +11558,7 @@
     </row>
     <row r="379" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U379" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V379" t="s">
         <v>768</v>
@@ -11575,7 +11572,7 @@
     </row>
     <row r="380" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U380" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V380" t="s">
         <v>769</v>
@@ -11589,7 +11586,7 @@
     </row>
     <row r="381" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U381" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V381" t="s">
         <v>771</v>
@@ -11603,7 +11600,7 @@
     </row>
     <row r="382" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U382" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V382" t="s">
         <v>772</v>
@@ -11617,7 +11614,7 @@
     </row>
     <row r="383" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U383" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V383" t="s">
         <v>773</v>
@@ -11631,7 +11628,7 @@
     </row>
     <row r="384" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U384" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V384" t="s">
         <v>774</v>
@@ -11645,7 +11642,7 @@
     </row>
     <row r="385" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U385" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V385" t="s">
         <v>775</v>
@@ -11659,7 +11656,7 @@
     </row>
     <row r="386" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U386" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V386" t="s">
         <v>776</v>
@@ -11673,7 +11670,7 @@
     </row>
     <row r="387" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U387" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V387" t="s">
         <v>777</v>
@@ -11687,7 +11684,7 @@
     </row>
     <row r="388" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U388" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V388" t="s">
         <v>778</v>
@@ -11701,7 +11698,7 @@
     </row>
     <row r="389" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U389" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V389" t="s">
         <v>779</v>
@@ -11715,7 +11712,7 @@
     </row>
     <row r="390" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U390" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V390" t="s">
         <v>780</v>
@@ -11729,7 +11726,7 @@
     </row>
     <row r="391" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U391" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V391" t="s">
         <v>781</v>
@@ -11743,7 +11740,7 @@
     </row>
     <row r="392" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U392" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V392" t="s">
         <v>782</v>
@@ -11757,7 +11754,7 @@
     </row>
     <row r="393" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U393" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V393" t="s">
         <v>783</v>
@@ -11771,7 +11768,7 @@
     </row>
     <row r="394" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U394" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V394" t="s">
         <v>784</v>
@@ -11785,7 +11782,7 @@
     </row>
     <row r="395" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U395" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V395" t="s">
         <v>785</v>
@@ -11799,7 +11796,7 @@
     </row>
     <row r="396" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U396" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V396" t="s">
         <v>786</v>
@@ -11813,7 +11810,7 @@
     </row>
     <row r="397" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U397" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V397" t="s">
         <v>787</v>
@@ -11827,7 +11824,7 @@
     </row>
     <row r="398" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U398" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V398" t="s">
         <v>788</v>
@@ -11841,7 +11838,7 @@
     </row>
     <row r="399" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U399" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V399" t="s">
         <v>789</v>
@@ -11855,7 +11852,7 @@
     </row>
     <row r="400" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U400" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V400" t="s">
         <v>790</v>
@@ -11869,7 +11866,7 @@
     </row>
     <row r="401" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U401" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V401" t="s">
         <v>791</v>
@@ -11883,7 +11880,7 @@
     </row>
     <row r="402" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U402" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V402" t="s">
         <v>792</v>
@@ -11897,7 +11894,7 @@
     </row>
     <row r="403" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U403" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V403" t="s">
         <v>793</v>
@@ -11911,7 +11908,7 @@
     </row>
     <row r="404" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U404" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V404" t="s">
         <v>794</v>
@@ -11925,7 +11922,7 @@
     </row>
     <row r="405" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U405" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V405" t="s">
         <v>795</v>
@@ -11939,7 +11936,7 @@
     </row>
     <row r="406" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U406" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V406" t="s">
         <v>796</v>
@@ -11953,7 +11950,7 @@
     </row>
     <row r="407" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U407" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V407" t="s">
         <v>797</v>
@@ -11967,7 +11964,7 @@
     </row>
     <row r="408" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U408" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V408" t="s">
         <v>798</v>
@@ -11981,7 +11978,7 @@
     </row>
     <row r="409" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U409" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V409" t="s">
         <v>799</v>
@@ -11995,7 +11992,7 @@
     </row>
     <row r="410" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U410" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V410" t="s">
         <v>800</v>
@@ -12009,7 +12006,7 @@
     </row>
     <row r="411" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U411" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V411" t="s">
         <v>801</v>
@@ -12023,7 +12020,7 @@
     </row>
     <row r="412" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U412" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V412" t="s">
         <v>802</v>
@@ -12037,7 +12034,7 @@
     </row>
     <row r="413" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U413" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V413" t="s">
         <v>803</v>
@@ -12051,7 +12048,7 @@
     </row>
     <row r="414" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U414" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V414" t="s">
         <v>804</v>
@@ -12065,7 +12062,7 @@
     </row>
     <row r="415" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U415" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V415" t="s">
         <v>805</v>
@@ -12079,7 +12076,7 @@
     </row>
     <row r="416" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U416" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V416" t="s">
         <v>806</v>
@@ -12093,7 +12090,7 @@
     </row>
     <row r="417" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U417" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V417" t="s">
         <v>807</v>
@@ -12107,7 +12104,7 @@
     </row>
     <row r="418" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U418" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V418" t="s">
         <v>808</v>
@@ -12121,7 +12118,7 @@
     </row>
     <row r="419" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U419" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V419" t="s">
         <v>809</v>
@@ -12135,7 +12132,7 @@
     </row>
     <row r="420" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U420" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V420" t="s">
         <v>810</v>
@@ -12149,7 +12146,7 @@
     </row>
     <row r="421" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U421" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V421" t="s">
         <v>811</v>
@@ -12163,7 +12160,7 @@
     </row>
     <row r="422" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U422" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V422" t="s">
         <v>812</v>
@@ -12177,7 +12174,7 @@
     </row>
     <row r="423" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U423" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V423" t="s">
         <v>814</v>
@@ -12191,7 +12188,7 @@
     </row>
     <row r="424" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U424" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V424" t="s">
         <v>815</v>
@@ -12205,7 +12202,7 @@
     </row>
     <row r="425" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U425" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V425" t="s">
         <v>817</v>
@@ -12219,7 +12216,7 @@
     </row>
     <row r="426" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U426" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V426" t="s">
         <v>818</v>
@@ -12233,7 +12230,7 @@
     </row>
     <row r="427" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U427" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V427" t="s">
         <v>820</v>
@@ -12247,7 +12244,7 @@
     </row>
     <row r="428" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U428" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V428" t="s">
         <v>821</v>
@@ -12261,7 +12258,7 @@
     </row>
     <row r="429" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U429" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V429" t="s">
         <v>822</v>
@@ -12275,7 +12272,7 @@
     </row>
     <row r="430" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U430" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V430" t="s">
         <v>823</v>
@@ -12289,7 +12286,7 @@
     </row>
     <row r="431" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U431" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V431" t="s">
         <v>824</v>
@@ -12303,7 +12300,7 @@
     </row>
     <row r="432" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U432" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V432" t="s">
         <v>825</v>
@@ -12317,7 +12314,7 @@
     </row>
     <row r="433" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U433" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V433" t="s">
         <v>826</v>
@@ -12331,7 +12328,7 @@
     </row>
     <row r="434" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U434" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V434" t="s">
         <v>827</v>
@@ -12345,7 +12342,7 @@
     </row>
     <row r="435" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U435" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V435" t="s">
         <v>828</v>
@@ -12359,7 +12356,7 @@
     </row>
     <row r="436" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U436" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V436" t="s">
         <v>829</v>
@@ -12373,7 +12370,7 @@
     </row>
     <row r="437" spans="21:24" x14ac:dyDescent="0.45">
       <c r="U437" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="V437" t="s">
         <v>830</v>
@@ -12391,48 +12388,48 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352419E0-7ADB-40EA-9452-7B95EFBD4692}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F015905D-5057-48CD-8C4E-69C0E9624146}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" t="s">
         <v>93</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>94</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>95</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>96</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>97</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>98</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>99</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>100</v>
       </c>
-      <c r="J10" t="s">
+      <c r="L10" t="s">
         <v>101</v>
-      </c>
-      <c r="K10" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12440,34 +12437,34 @@
         <v>2030</v>
       </c>
       <c r="C11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11">
+        <v>33.363999999999997</v>
+      </c>
+      <c r="F11" t="s">
         <v>104</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" t="s">
         <v>105</v>
       </c>
-      <c r="E11">
-        <v>333.64</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>106</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J11" t="s">
         <v>107</v>
       </c>
-      <c r="H11" t="s">
+      <c r="K11" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="L11" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12475,34 +12472,34 @@
         <v>2030</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>4.5999999999999996</v>
       </c>
       <c r="F12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" t="s">
         <v>106</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J12" t="s">
         <v>107</v>
       </c>
-      <c r="H12" t="s">
+      <c r="K12" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I12" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="L12" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12510,34 +12507,34 @@
         <v>2030</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E13">
         <v>1.86</v>
       </c>
       <c r="F13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" t="s">
         <v>106</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J13" t="s">
         <v>107</v>
       </c>
-      <c r="H13" t="s">
+      <c r="K13" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I13" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="L13" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12545,34 +12542,34 @@
         <v>2030</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>6.38</v>
       </c>
       <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" t="s">
         <v>106</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J14" t="s">
         <v>107</v>
       </c>
-      <c r="H14" t="s">
+      <c r="K14" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="L14" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12580,34 +12577,34 @@
         <v>2030</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E15">
         <v>8.2880000000000003</v>
       </c>
       <c r="F15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" t="s">
         <v>106</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J15" t="s">
         <v>107</v>
       </c>
-      <c r="H15" t="s">
+      <c r="K15" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="L15" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12615,34 +12612,34 @@
         <v>2030</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E16">
         <v>17.742000000000001</v>
       </c>
       <c r="F16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" t="s">
         <v>106</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J16" t="s">
         <v>107</v>
       </c>
-      <c r="H16" t="s">
+      <c r="K16" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="L16" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12650,34 +12647,34 @@
         <v>2030</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E17">
         <v>300</v>
       </c>
       <c r="F17" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" t="s">
         <v>106</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J17" t="s">
         <v>107</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="L17" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12685,34 +12682,34 @@
         <v>2030</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E18">
         <v>58.8</v>
       </c>
       <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" t="s">
         <v>106</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J18" t="s">
         <v>107</v>
       </c>
-      <c r="H18" t="s">
+      <c r="K18" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J18" t="s">
+      <c r="L18" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12720,34 +12717,34 @@
         <v>2030</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E19">
         <v>8.4</v>
       </c>
       <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" t="s">
         <v>106</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J19" t="s">
         <v>107</v>
       </c>
-      <c r="H19" t="s">
+      <c r="K19" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I19" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="L19" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12755,34 +12752,34 @@
         <v>2030</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E20">
         <v>4.5</v>
       </c>
       <c r="F20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" t="s">
         <v>106</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J20" t="s">
         <v>107</v>
       </c>
-      <c r="H20" t="s">
+      <c r="K20" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="L20" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12790,34 +12787,34 @@
         <v>2030</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E21">
         <v>1.3</v>
       </c>
       <c r="F21" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" t="s">
         <v>106</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J21" t="s">
         <v>107</v>
       </c>
-      <c r="H21" t="s">
+      <c r="K21" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I21" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="L21" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="22" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12825,34 +12822,34 @@
         <v>2030</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E22">
         <v>6.3</v>
       </c>
       <c r="F22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" t="s">
+        <v>105</v>
+      </c>
+      <c r="H22" t="s">
         <v>106</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J22" t="s">
         <v>107</v>
       </c>
-      <c r="H22" t="s">
+      <c r="K22" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I22" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J22" t="s">
+      <c r="L22" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
@@ -12860,34 +12857,34 @@
         <v>2030</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E23">
         <v>17.8</v>
       </c>
       <c r="F23" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" t="s">
+        <v>105</v>
+      </c>
+      <c r="H23" t="s">
         <v>106</v>
       </c>
-      <c r="G23" t="s">
+      <c r="I23" s="13">
+        <v>43755</v>
+      </c>
+      <c r="J23" t="s">
         <v>107</v>
       </c>
-      <c r="H23" t="s">
+      <c r="K23" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I23" s="14">
-        <v>43755</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="L23" s="14" t="s">
         <v>109</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -13010,7 +13007,7 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
@@ -13033,7 +13030,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -13066,7 +13063,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -13287,7 +13284,7 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3">
         <v>1.7562346329469618E-2</v>
@@ -13302,7 +13299,7 @@
         <v>8.1281428819143395E-2</v>
       </c>
       <c r="AF10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="AG10" t="s">
         <v>23</v>
@@ -13315,7 +13312,7 @@
         <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AJ10" s="12">
         <f>AI10*$AD$1</f>
         <v>0</v>
       </c>
@@ -13337,7 +13334,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -13413,7 +13410,7 @@
         <v>1.94</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -13635,7 +13632,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -13650,7 +13647,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A10:J23"/>
+  <dimension ref="A9:J23"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
@@ -13665,62 +13662,67 @@
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="2:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="8" t="s">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="I10" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="J10" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="12">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="B11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="E11" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="12">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12">
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>0.05</v>
+      </c>
+      <c r="H11">
+        <v>0.1</v>
+      </c>
+      <c r="I11">
         <v>0</v>
       </c>
-      <c r="H11" s="12">
-        <v>1</v>
-      </c>
-      <c r="I11" s="12">
-        <v>0</v>
-      </c>
-      <c r="J11" s="12">
-        <v>1</v>
+      <c r="J11">
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.45">
@@ -13730,7 +13732,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -13738,16 +13740,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -13772,18 +13774,18 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
         <f>C11</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <f>D11</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -13802,18 +13804,18 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
         <f>E11</f>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G21">
         <f>F11</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -13832,18 +13834,18 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
         <f>G11</f>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G22">
         <f>H11</f>
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -13862,7 +13864,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -13873,7 +13875,7 @@
       </c>
       <c r="G23">
         <f>J11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -17363,7 +17365,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B249">
         <v>2000</v>
@@ -17475,7 +17477,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B257">
         <v>2001</v>
@@ -17587,7 +17589,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B265">
         <v>2002</v>
@@ -17699,7 +17701,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B273">
         <v>2003</v>
@@ -17811,7 +17813,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B281">
         <v>2004</v>
@@ -17923,7 +17925,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B289">
         <v>2005</v>
@@ -18035,7 +18037,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B297">
         <v>2006</v>
@@ -18147,7 +18149,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B305">
         <v>2007</v>
@@ -18259,7 +18261,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B313">
         <v>2008</v>
@@ -18371,7 +18373,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B321">
         <v>2009</v>
@@ -18483,7 +18485,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B329">
         <v>2010</v>
@@ -18595,7 +18597,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B337">
         <v>2011</v>
@@ -18707,7 +18709,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B345">
         <v>2012</v>
@@ -18819,7 +18821,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B353">
         <v>2013</v>
@@ -18931,7 +18933,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B361">
         <v>2014</v>
@@ -19043,7 +19045,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B369">
         <v>2015</v>
@@ -19155,7 +19157,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B377">
         <v>2016</v>
@@ -19267,7 +19269,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B385">
         <v>2017</v>
@@ -19379,7 +19381,7 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B393">
         <v>2018</v>
@@ -19491,7 +19493,7 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B401">
         <v>2019</v>
@@ -19603,7 +19605,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B409">
         <v>2020</v>
@@ -19715,7 +19717,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B417">
         <v>2021</v>
@@ -19827,7 +19829,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B425">
         <v>2022</v>
@@ -19939,7 +19941,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -20681,7 +20683,7 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B486">
         <v>2018</v>
@@ -20695,7 +20697,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B487">
         <v>2019</v>
@@ -20709,7 +20711,7 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B488">
         <v>2020</v>
@@ -20723,7 +20725,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B489">
         <v>2021</v>
@@ -20737,7 +20739,7 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B490">
         <v>2022</v>
@@ -20751,7 +20753,7 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B491">
         <v>2023</v>
@@ -20765,7 +20767,7 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B492">
         <v>2024</v>
@@ -20779,7 +20781,7 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B493">
         <v>2011</v>
@@ -20793,7 +20795,7 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B494">
         <v>2012</v>
@@ -20807,7 +20809,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B495">
         <v>2013</v>
@@ -20821,7 +20823,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B496">
         <v>2014</v>
@@ -20835,7 +20837,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B497">
         <v>2015</v>
@@ -20849,7 +20851,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B498">
         <v>2016</v>
@@ -20863,7 +20865,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B499">
         <v>2017</v>
@@ -20877,7 +20879,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B500">
         <v>2004</v>
@@ -20891,7 +20893,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B501">
         <v>2005</v>
@@ -20905,7 +20907,7 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B502">
         <v>2006</v>
@@ -20919,7 +20921,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B503">
         <v>2007</v>
@@ -20933,7 +20935,7 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B504">
         <v>2008</v>
@@ -20947,7 +20949,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B505">
         <v>2009</v>
@@ -20961,7 +20963,7 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B506">
         <v>2010</v>
@@ -20975,7 +20977,7 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B507">
         <v>2002</v>
@@ -20989,7 +20991,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B508">
         <v>2003</v>
@@ -21003,7 +21005,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B509">
         <v>2005</v>
@@ -21017,7 +21019,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B510">
         <v>2006</v>
@@ -21031,7 +21033,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B511">
         <v>2007</v>
@@ -21045,7 +21047,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B512">
         <v>2008</v>
@@ -21059,7 +21061,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B513">
         <v>2009</v>
@@ -21073,7 +21075,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B514">
         <v>2010</v>
@@ -21087,7 +21089,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B515">
         <v>2011</v>
@@ -21101,7 +21103,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B516">
         <v>2012</v>
@@ -21115,7 +21117,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B517">
         <v>2013</v>
@@ -21129,7 +21131,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B518">
         <v>2014</v>
@@ -21143,7 +21145,7 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B519">
         <v>2015</v>
@@ -21157,7 +21159,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B520">
         <v>2016</v>
@@ -21171,7 +21173,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B521">
         <v>2017</v>
@@ -21185,7 +21187,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B522">
         <v>2018</v>
@@ -21199,7 +21201,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B523">
         <v>2019</v>
@@ -21213,7 +21215,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B524">
         <v>2020</v>
@@ -21227,7 +21229,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B525">
         <v>2021</v>
@@ -21241,7 +21243,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B526">
         <v>2022</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE7BBF4C-2437-4E7E-939F-A9D5BA12BB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E10E4644-394F-4610-89C8-A35B65E7D5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3139,7 +3139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F97870A7-AF66-45E8-BF7F-3FE6D95B5BA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E396EA-DF30-4D68-9CE2-AF62AB009884}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12388,7 +12388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F015905D-5057-48CD-8C4E-69C0E9624146}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB248F41-2001-4FE2-9841-0DDEBA74A0B4}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E10E4644-394F-4610-89C8-A35B65E7D5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD5F6993-40A5-46B7-88E3-F5C8CAC1682D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3139,7 +3139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E396EA-DF30-4D68-9CE2-AF62AB009884}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12388,7 +12388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB248F41-2001-4FE2-9841-0DDEBA74A0B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DAD033-34FF-4018-A513-09ED2390787C}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD5F6993-40A5-46B7-88E3-F5C8CAC1682D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21CB483F-9B7F-4336-A9B5-FC29426E00EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3139,7 +3139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B043D5-3B5B-4509-93B5-F4D229BE8B7C}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12388,7 +12388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DAD033-34FF-4018-A513-09ED2390787C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BFEA91-1E73-4505-847E-49C9CC4544A5}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21CB483F-9B7F-4336-A9B5-FC29426E00EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD5F6993-40A5-46B7-88E3-F5C8CAC1682D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3139,7 +3139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B043D5-3B5B-4509-93B5-F4D229BE8B7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12388,7 +12388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BFEA91-1E73-4505-847E-49C9CC4544A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DAD033-34FF-4018-A513-09ED2390787C}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD5F6993-40A5-46B7-88E3-F5C8CAC1682D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C5CEF3-C6D6-4333-834F-6F26D722DECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3139,7 +3139,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DFD2E8-75A5-4300-ADD2-23CA2829A993}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12388,7 +12388,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DAD033-34FF-4018-A513-09ED2390787C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A166A1-E9B1-4D99-B099-036AFC817F58}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C5CEF3-C6D6-4333-834F-6F26D722DECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD552F5-C95D-477C-A519-5919F55A5A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3773" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="843">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2648,6 +2648,15 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>NCAP_START</t>
+  </si>
+  <si>
+    <t>-co2cap*</t>
+  </si>
+  <si>
+    <t>COAL</t>
   </si>
 </sst>
 </file>
@@ -2658,7 +2667,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2724,8 +2733,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2749,8 +2766,14 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2776,6 +2799,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFF7800"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFF7800"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF7800"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFF7800"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF7800"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFF7800"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFF7800"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFF7800"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2784,7 +2844,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2802,6 +2862,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
@@ -3139,7 +3205,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DFD2E8-75A5-4300-ADD2-23CA2829A993}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
   <dimension ref="B2:AF437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12388,7 +12454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A166A1-E9B1-4D99-B099-036AFC817F58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DAD033-34FF-4018-A513-09ED2390787C}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13647,12 +13713,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
-  <dimension ref="A9:J23"/>
+  <dimension ref="A9:J31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.265625" customWidth="1"/>
-    <col min="3" max="3" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.06640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.73046875" bestFit="1" customWidth="1"/>
@@ -13881,8 +13947,43 @@
         <v>4</v>
       </c>
     </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B28" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B29" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B30" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>841</v>
+      </c>
+      <c r="D30" s="19">
+        <v>2100</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD552F5-C95D-477C-A519-5919F55A5A9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FB5CCB-CF77-4046-81EE-4989AE0BB875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
-    <sheet name="Veda" sheetId="1" r:id="rId3"/>
-    <sheet name="buildrates" sheetId="4" r:id="rId4"/>
-    <sheet name="historical_data_long" sheetId="3" r:id="rId5"/>
+    <sheet name="vre agg cap" sheetId="7" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId3"/>
+    <sheet name="Veda" sheetId="1" r:id="rId4"/>
+    <sheet name="buildrates" sheetId="4" r:id="rId5"/>
+    <sheet name="historical_data_long" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -125,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3781" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3896" uniqueCount="952">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2657,6 +2658,333 @@
   </si>
   <si>
     <t>COAL</t>
+  </si>
+  <si>
+    <t>~UC_Sets: R_S: Allregions</t>
+  </si>
+  <si>
+    <t>~UC_T</t>
+  </si>
+  <si>
+    <t>uc_cap</t>
+  </si>
+  <si>
+    <t>uc_rhst~0</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_014</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_021</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_040</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_043</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_042</t>
   </si>
 </sst>
 </file>
@@ -12454,6 +12782,2791 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8E1348-6DD1-4555-B7B4-7AB70C2A26E6}">
+  <dimension ref="B1:I109"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.53125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C1" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>845</v>
+      </c>
+      <c r="E4" t="s">
+        <v>846</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B5" t="str">
+        <f>"UCE_elcagg_"&amp;MID(C5,5,32)</f>
+        <v>UCE_elcagg_spv_ZAF_001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>847</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="str">
+        <f>B5</f>
+        <v>UCE_elcagg_spv_ZAF_001</v>
+      </c>
+      <c r="H5" t="str">
+        <f>C5</f>
+        <v>elc_spv_ZAF_001</v>
+      </c>
+      <c r="I5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B6" t="str">
+        <f t="shared" ref="B6:B69" si="0">"UCE_elcagg_"&amp;MID(C6,5,32)</f>
+        <v>UCE_elcagg_spv_ZAF_002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>848</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" ref="G6:G16" si="1">B6</f>
+        <v>UCE_elcagg_spv_ZAF_002</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" ref="H6:H16" si="2">C6</f>
+        <v>elc_spv_ZAF_002</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>849</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_003</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_003</v>
+      </c>
+      <c r="I7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>850</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_004</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_004</v>
+      </c>
+      <c r="I8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>851</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_005</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_005</v>
+      </c>
+      <c r="I9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>852</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_006</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_006</v>
+      </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>853</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_007</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_007</v>
+      </c>
+      <c r="I11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>854</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_008</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_008</v>
+      </c>
+      <c r="I12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>855</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_009</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_009</v>
+      </c>
+      <c r="I13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>856</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_010</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_010</v>
+      </c>
+      <c r="I14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>857</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_011</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_011</v>
+      </c>
+      <c r="I15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>858</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="str">
+        <f t="shared" si="1"/>
+        <v>UCE_elcagg_spv_ZAF_012</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="2"/>
+        <v>elc_spv_ZAF_012</v>
+      </c>
+      <c r="I16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>859</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="str">
+        <f t="shared" ref="G17:G80" si="3">B17</f>
+        <v>UCE_elcagg_spv_ZAF_013</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" ref="H17:H80" si="4">C17</f>
+        <v>elc_spv_ZAF_013</v>
+      </c>
+      <c r="I17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>860</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_014</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_014</v>
+      </c>
+      <c r="I18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>861</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_015</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_015</v>
+      </c>
+      <c r="I19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>862</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_016</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_016</v>
+      </c>
+      <c r="I20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>863</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_017</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_017</v>
+      </c>
+      <c r="I21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>864</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_018</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_018</v>
+      </c>
+      <c r="I22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>865</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_019</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_019</v>
+      </c>
+      <c r="I23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>866</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_020</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_020</v>
+      </c>
+      <c r="I24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_021</v>
+      </c>
+      <c r="C25" t="s">
+        <v>867</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_021</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_021</v>
+      </c>
+      <c r="I25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>868</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_022</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_022</v>
+      </c>
+      <c r="I26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_023</v>
+      </c>
+      <c r="C27" t="s">
+        <v>869</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_023</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_023</v>
+      </c>
+      <c r="I27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_024</v>
+      </c>
+      <c r="C28" t="s">
+        <v>870</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_024</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_024</v>
+      </c>
+      <c r="I28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_025</v>
+      </c>
+      <c r="C29" t="s">
+        <v>871</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_025</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_025</v>
+      </c>
+      <c r="I29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_026</v>
+      </c>
+      <c r="C30" t="s">
+        <v>872</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_026</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_026</v>
+      </c>
+      <c r="I30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_027</v>
+      </c>
+      <c r="C31" t="s">
+        <v>873</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_027</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_027</v>
+      </c>
+      <c r="I31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_028</v>
+      </c>
+      <c r="C32" t="s">
+        <v>874</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_028</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_028</v>
+      </c>
+      <c r="I32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_029</v>
+      </c>
+      <c r="C33" t="s">
+        <v>875</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_029</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_029</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_030</v>
+      </c>
+      <c r="C34" t="s">
+        <v>876</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_030</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_030</v>
+      </c>
+      <c r="I34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_031</v>
+      </c>
+      <c r="C35" t="s">
+        <v>877</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_031</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_031</v>
+      </c>
+      <c r="I35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_032</v>
+      </c>
+      <c r="C36" t="s">
+        <v>878</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_032</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_032</v>
+      </c>
+      <c r="I36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_033</v>
+      </c>
+      <c r="C37" t="s">
+        <v>879</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_033</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_033</v>
+      </c>
+      <c r="I37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_034</v>
+      </c>
+      <c r="C38" t="s">
+        <v>880</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_034</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_034</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_035</v>
+      </c>
+      <c r="C39" t="s">
+        <v>881</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_035</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_035</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_036</v>
+      </c>
+      <c r="C40" t="s">
+        <v>882</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_036</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_036</v>
+      </c>
+      <c r="I40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_037</v>
+      </c>
+      <c r="C41" t="s">
+        <v>883</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_037</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_037</v>
+      </c>
+      <c r="I41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_038</v>
+      </c>
+      <c r="C42" t="s">
+        <v>884</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_038</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_038</v>
+      </c>
+      <c r="I42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_039</v>
+      </c>
+      <c r="C43" t="s">
+        <v>885</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_039</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_039</v>
+      </c>
+      <c r="I43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_040</v>
+      </c>
+      <c r="C44" t="s">
+        <v>886</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_040</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_040</v>
+      </c>
+      <c r="I44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_041</v>
+      </c>
+      <c r="C45" t="s">
+        <v>887</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_041</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_041</v>
+      </c>
+      <c r="I45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_042</v>
+      </c>
+      <c r="C46" t="s">
+        <v>888</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_042</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_042</v>
+      </c>
+      <c r="I46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_spv_ZAF_043</v>
+      </c>
+      <c r="C47" t="s">
+        <v>889</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_spv_ZAF_043</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_spv_ZAF_043</v>
+      </c>
+      <c r="I47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_001</v>
+      </c>
+      <c r="C48" t="s">
+        <v>890</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_001</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_001</v>
+      </c>
+      <c r="I48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_002</v>
+      </c>
+      <c r="C49" t="s">
+        <v>891</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_002</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_002</v>
+      </c>
+      <c r="I49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_003</v>
+      </c>
+      <c r="C50" t="s">
+        <v>892</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_003</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_003</v>
+      </c>
+      <c r="I50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_004</v>
+      </c>
+      <c r="C51" t="s">
+        <v>893</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_004</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_004</v>
+      </c>
+      <c r="I51">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_005</v>
+      </c>
+      <c r="C52" t="s">
+        <v>894</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_005</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_005</v>
+      </c>
+      <c r="I52">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_006</v>
+      </c>
+      <c r="C53" t="s">
+        <v>895</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_006</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_006</v>
+      </c>
+      <c r="I53">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_007</v>
+      </c>
+      <c r="C54" t="s">
+        <v>896</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_007</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_007</v>
+      </c>
+      <c r="I54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_008</v>
+      </c>
+      <c r="C55" t="s">
+        <v>897</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_008</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_008</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_009</v>
+      </c>
+      <c r="C56" t="s">
+        <v>898</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_009</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_009</v>
+      </c>
+      <c r="I56">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_010</v>
+      </c>
+      <c r="C57" t="s">
+        <v>899</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_010</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_010</v>
+      </c>
+      <c r="I57">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_011</v>
+      </c>
+      <c r="C58" t="s">
+        <v>900</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_011</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_011</v>
+      </c>
+      <c r="I58">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_012</v>
+      </c>
+      <c r="C59" t="s">
+        <v>901</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_012</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_012</v>
+      </c>
+      <c r="I59">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_013</v>
+      </c>
+      <c r="C60" t="s">
+        <v>902</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60">
+        <v>2</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_013</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_013</v>
+      </c>
+      <c r="I60">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B61" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_014</v>
+      </c>
+      <c r="C61" t="s">
+        <v>903</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_014</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_014</v>
+      </c>
+      <c r="I61">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B62" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_015</v>
+      </c>
+      <c r="C62" t="s">
+        <v>904</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_015</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_015</v>
+      </c>
+      <c r="I62">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B63" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_016</v>
+      </c>
+      <c r="C63" t="s">
+        <v>905</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_016</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_016</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B64" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_017</v>
+      </c>
+      <c r="C64" t="s">
+        <v>906</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_017</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_017</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B65" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_018</v>
+      </c>
+      <c r="C65" t="s">
+        <v>907</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_018</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_018</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B66" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_019</v>
+      </c>
+      <c r="C66" t="s">
+        <v>908</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_019</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_019</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B67" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_wof_ZAF_020</v>
+      </c>
+      <c r="C67" t="s">
+        <v>909</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="G67" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_wof_ZAF_020</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_wof_ZAF_020</v>
+      </c>
+      <c r="I67">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B68" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_won_ZAF_001</v>
+      </c>
+      <c r="C68" t="s">
+        <v>910</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_001</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_001</v>
+      </c>
+      <c r="I68">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B69" t="str">
+        <f t="shared" si="0"/>
+        <v>UCE_elcagg_won_ZAF_002</v>
+      </c>
+      <c r="C69" t="s">
+        <v>911</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="G69" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_002</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_002</v>
+      </c>
+      <c r="I69">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B70" t="str">
+        <f t="shared" ref="B70:B109" si="5">"UCE_elcagg_"&amp;MID(C70,5,32)</f>
+        <v>UCE_elcagg_won_ZAF_003</v>
+      </c>
+      <c r="C70" t="s">
+        <v>912</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_003</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_003</v>
+      </c>
+      <c r="I70">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B71" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_004</v>
+      </c>
+      <c r="C71" t="s">
+        <v>913</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_004</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_004</v>
+      </c>
+      <c r="I71">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B72" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_005</v>
+      </c>
+      <c r="C72" t="s">
+        <v>914</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_005</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_005</v>
+      </c>
+      <c r="I72">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B73" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_006</v>
+      </c>
+      <c r="C73" t="s">
+        <v>915</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="G73" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_006</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_006</v>
+      </c>
+      <c r="I73">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B74" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_007</v>
+      </c>
+      <c r="C74" t="s">
+        <v>916</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="G74" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_007</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_007</v>
+      </c>
+      <c r="I74">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B75" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_008</v>
+      </c>
+      <c r="C75" t="s">
+        <v>917</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="G75" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_008</v>
+      </c>
+      <c r="H75" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_008</v>
+      </c>
+      <c r="I75">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B76" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_009</v>
+      </c>
+      <c r="C76" t="s">
+        <v>918</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_009</v>
+      </c>
+      <c r="H76" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_009</v>
+      </c>
+      <c r="I76">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B77" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_010</v>
+      </c>
+      <c r="C77" t="s">
+        <v>919</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="G77" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_010</v>
+      </c>
+      <c r="H77" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_010</v>
+      </c>
+      <c r="I77">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B78" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_011</v>
+      </c>
+      <c r="C78" t="s">
+        <v>920</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="G78" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_011</v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_011</v>
+      </c>
+      <c r="I78">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B79" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_012</v>
+      </c>
+      <c r="C79" t="s">
+        <v>921</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>2</v>
+      </c>
+      <c r="G79" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_012</v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_012</v>
+      </c>
+      <c r="I79">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B80" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_013</v>
+      </c>
+      <c r="C80" t="s">
+        <v>922</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="G80" t="str">
+        <f t="shared" si="3"/>
+        <v>UCE_elcagg_won_ZAF_013</v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="4"/>
+        <v>elc_won_ZAF_013</v>
+      </c>
+      <c r="I80">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B81" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_014</v>
+      </c>
+      <c r="C81" t="s">
+        <v>923</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="G81" t="str">
+        <f t="shared" ref="G81:G109" si="6">B81</f>
+        <v>UCE_elcagg_won_ZAF_014</v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" ref="H81:H109" si="7">C81</f>
+        <v>elc_won_ZAF_014</v>
+      </c>
+      <c r="I81">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B82" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_015</v>
+      </c>
+      <c r="C82" t="s">
+        <v>924</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="G82" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_015</v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_015</v>
+      </c>
+      <c r="I82">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B83" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_016</v>
+      </c>
+      <c r="C83" t="s">
+        <v>925</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="G83" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_016</v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_016</v>
+      </c>
+      <c r="I83">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B84" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_017</v>
+      </c>
+      <c r="C84" t="s">
+        <v>926</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="G84" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_017</v>
+      </c>
+      <c r="H84" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_017</v>
+      </c>
+      <c r="I84">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B85" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_018</v>
+      </c>
+      <c r="C85" t="s">
+        <v>927</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
+      </c>
+      <c r="G85" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_018</v>
+      </c>
+      <c r="H85" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_018</v>
+      </c>
+      <c r="I85">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B86" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_019</v>
+      </c>
+      <c r="C86" t="s">
+        <v>928</v>
+      </c>
+      <c r="D86">
+        <v>1</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="G86" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_019</v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_019</v>
+      </c>
+      <c r="I86">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B87" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_020</v>
+      </c>
+      <c r="C87" t="s">
+        <v>929</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="G87" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_020</v>
+      </c>
+      <c r="H87" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_020</v>
+      </c>
+      <c r="I87">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B88" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_021</v>
+      </c>
+      <c r="C88" t="s">
+        <v>930</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="G88" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_021</v>
+      </c>
+      <c r="H88" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_021</v>
+      </c>
+      <c r="I88">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B89" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_022</v>
+      </c>
+      <c r="C89" t="s">
+        <v>931</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="G89" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_022</v>
+      </c>
+      <c r="H89" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_022</v>
+      </c>
+      <c r="I89">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B90" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_023</v>
+      </c>
+      <c r="C90" t="s">
+        <v>932</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="G90" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_023</v>
+      </c>
+      <c r="H90" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_023</v>
+      </c>
+      <c r="I90">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B91" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_024</v>
+      </c>
+      <c r="C91" t="s">
+        <v>933</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="G91" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_024</v>
+      </c>
+      <c r="H91" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_024</v>
+      </c>
+      <c r="I91">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B92" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_025</v>
+      </c>
+      <c r="C92" t="s">
+        <v>934</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>2</v>
+      </c>
+      <c r="G92" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_025</v>
+      </c>
+      <c r="H92" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_025</v>
+      </c>
+      <c r="I92">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B93" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_026</v>
+      </c>
+      <c r="C93" t="s">
+        <v>935</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>2</v>
+      </c>
+      <c r="G93" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_026</v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_026</v>
+      </c>
+      <c r="I93">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B94" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_027</v>
+      </c>
+      <c r="C94" t="s">
+        <v>936</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+      <c r="G94" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_027</v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_027</v>
+      </c>
+      <c r="I94">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B95" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_028</v>
+      </c>
+      <c r="C95" t="s">
+        <v>937</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="G95" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_028</v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_028</v>
+      </c>
+      <c r="I95">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B96" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_029</v>
+      </c>
+      <c r="C96" t="s">
+        <v>938</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_029</v>
+      </c>
+      <c r="H96" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_029</v>
+      </c>
+      <c r="I96">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B97" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_030</v>
+      </c>
+      <c r="C97" t="s">
+        <v>939</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="G97" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_030</v>
+      </c>
+      <c r="H97" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_030</v>
+      </c>
+      <c r="I97">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B98" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_031</v>
+      </c>
+      <c r="C98" t="s">
+        <v>940</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_031</v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_031</v>
+      </c>
+      <c r="I98">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B99" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_032</v>
+      </c>
+      <c r="C99" t="s">
+        <v>941</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_032</v>
+      </c>
+      <c r="H99" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_032</v>
+      </c>
+      <c r="I99">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B100" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_033</v>
+      </c>
+      <c r="C100" t="s">
+        <v>942</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_033</v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_033</v>
+      </c>
+      <c r="I100">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B101" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_034</v>
+      </c>
+      <c r="C101" t="s">
+        <v>943</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>2</v>
+      </c>
+      <c r="G101" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_034</v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_034</v>
+      </c>
+      <c r="I101">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B102" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_035</v>
+      </c>
+      <c r="C102" t="s">
+        <v>944</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>2</v>
+      </c>
+      <c r="G102" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_035</v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_035</v>
+      </c>
+      <c r="I102">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B103" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_036</v>
+      </c>
+      <c r="C103" t="s">
+        <v>945</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+      <c r="G103" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_036</v>
+      </c>
+      <c r="H103" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_036</v>
+      </c>
+      <c r="I103">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B104" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_037</v>
+      </c>
+      <c r="C104" t="s">
+        <v>946</v>
+      </c>
+      <c r="D104">
+        <v>1</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_037</v>
+      </c>
+      <c r="H104" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_037</v>
+      </c>
+      <c r="I104">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B105" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_038</v>
+      </c>
+      <c r="C105" t="s">
+        <v>947</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
+      </c>
+      <c r="G105" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_038</v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_038</v>
+      </c>
+      <c r="I105">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B106" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_039</v>
+      </c>
+      <c r="C106" t="s">
+        <v>948</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="G106" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_039</v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_039</v>
+      </c>
+      <c r="I106">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B107" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_040</v>
+      </c>
+      <c r="C107" t="s">
+        <v>949</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="G107" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_040</v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_040</v>
+      </c>
+      <c r="I107">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B108" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_041</v>
+      </c>
+      <c r="C108" t="s">
+        <v>950</v>
+      </c>
+      <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="G108" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_041</v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_041</v>
+      </c>
+      <c r="I108">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B109" t="str">
+        <f t="shared" si="5"/>
+        <v>UCE_elcagg_won_ZAF_042</v>
+      </c>
+      <c r="C109" t="s">
+        <v>951</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
+      </c>
+      <c r="G109" t="str">
+        <f t="shared" si="6"/>
+        <v>UCE_elcagg_won_ZAF_042</v>
+      </c>
+      <c r="H109" t="str">
+        <f t="shared" si="7"/>
+        <v>elc_won_ZAF_042</v>
+      </c>
+      <c r="I109">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DAD033-34FF-4018-A513-09ED2390787C}">
   <dimension ref="B9:L23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -12958,7 +16071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -13711,7 +16824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320A1887-1B0C-44A8-9658-90FD86FEE0A5}">
   <dimension ref="A9:J31"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -13987,7 +17100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC33DFE9-8C65-4A33-8FAE-96323628CE2A}">
   <dimension ref="A1:D656"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FB5CCB-CF77-4046-81EE-4989AE0BB875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC7E8C5-0E1D-4A9A-AB2E-8098B7139D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -16095,7 +16095,7 @@
     <col min="23" max="23" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="8.265625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="23.73046875" bestFit="1" customWidth="1"/>
@@ -16199,7 +16199,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>65535</v>
+        <v>0.9</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -16424,11 +16424,11 @@
       </c>
       <c r="Z9" s="2">
         <f>VLOOKUP(V9,$F$3:$J$11,3,FALSE)</f>
-        <v>65535</v>
+        <v>0.9</v>
       </c>
       <c r="AA9" s="2">
         <f>Z9*$AB$1</f>
-        <v>72088.5</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="AB9">
         <v>0</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A972B9-D6C2-4CB0-80F9-41643E85F47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5032E83-30B0-48EB-A451-C20EEB42ACED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="buildrates" sheetId="4" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">grids!$U$3:$X$437</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -126,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3884" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4284" uniqueCount="949">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2967,6 +2970,15 @@
   </si>
   <si>
     <t>elc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>AFC</t>
+  </si>
+  <si>
+    <t>~TFM_DINS-AT</t>
   </si>
 </sst>
 </file>
@@ -3516,10 +3528,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
-  <dimension ref="B2:AF437"/>
+  <dimension ref="B2:AP437"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="21" max="21" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="47.265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.06640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="32.796875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.1328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.06640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="31.1328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3532,8 +3555,14 @@
       <c r="U2" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG2" t="s">
+        <v>342</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="3" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3582,11 +3611,35 @@
       <c r="X3" t="s">
         <v>343</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="Z3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG3" t="s">
+        <v>354</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>301</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>343</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>301</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="4" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>118</v>
       </c>
@@ -3635,26 +3688,53 @@
       <c r="X4" t="s">
         <v>357</v>
       </c>
+      <c r="Z4" t="s">
+        <v>301</v>
+      </c>
       <c r="AA4" t="s">
-        <v>301</v>
+        <v>826</v>
       </c>
       <c r="AB4" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AC4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AD4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="AE4" t="s">
-        <v>830</v>
-      </c>
-      <c r="AF4" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>765</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>764</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM4" t="str">
+        <f>AH4</f>
+        <v>EN_STG4hbNREL_r17287657-400_ZAF</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO4" t="str">
+        <f>AI4</f>
+        <v>e_r17287657-400_ZAF</v>
+      </c>
+      <c r="AP4">
+        <f>4/24</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>119</v>
       </c>
@@ -3703,23 +3783,50 @@
       <c r="X5" t="s">
         <v>357</v>
       </c>
+      <c r="Z5" t="s">
+        <v>825</v>
+      </c>
       <c r="AA5" t="s">
-        <v>825</v>
-      </c>
-      <c r="AB5" t="s">
         <v>827</v>
       </c>
-      <c r="AC5">
+      <c r="AB5">
         <v>2</v>
       </c>
-      <c r="AE5">
+      <c r="AD5">
         <v>0</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AE5" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>820</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>731</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM5" t="str">
+        <f t="shared" ref="AM5:AM68" si="0">AH5</f>
+        <v>EN_STG4hbNREL_w102682082-400_ZAF</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO5" t="str">
+        <f t="shared" ref="AO5:AO68" si="1">AI5</f>
+        <v>e_w102682082-400_ZAF</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" ref="AP5:AP68" si="2">4/24</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>120</v>
       </c>
@@ -3768,23 +3875,50 @@
       <c r="X6" t="s">
         <v>357</v>
       </c>
+      <c r="Z6" t="s">
+        <v>825</v>
+      </c>
       <c r="AA6" t="s">
-        <v>825</v>
-      </c>
-      <c r="AB6" t="s">
         <v>827</v>
       </c>
+      <c r="AC6">
+        <v>2</v>
+      </c>
       <c r="AD6">
-        <v>2</v>
-      </c>
-      <c r="AE6">
         <v>0</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AE6" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>814</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>813</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM6" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w102925909-400_ZAF</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO6" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w102925909-400_ZAF</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="7" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>121</v>
       </c>
@@ -3833,8 +3967,35 @@
       <c r="X7" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG7" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>816</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>719</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM7" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w105759402-400_ZAF</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO7" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w105759402-400_ZAF</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="8" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>122</v>
       </c>
@@ -3883,8 +4044,35 @@
       <c r="X8" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>785</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>579</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM8" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w105811523-400_ZAF</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO8" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w105811523-400_ZAF</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>123</v>
       </c>
@@ -3933,8 +4121,35 @@
       <c r="X9" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>750</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM9" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w107391770-400_ZAF</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO9" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w107391770-400_ZAF</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="10" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>124</v>
       </c>
@@ -3983,8 +4198,35 @@
       <c r="X10" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>758</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>411</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM10" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w107431792-400_ZAF</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO10" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w107431792-400_ZAF</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="11" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>125</v>
       </c>
@@ -4033,8 +4275,35 @@
       <c r="X11" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG11" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>756</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>397</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM11" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w120941269-400_ZAF</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO11" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w120941269-400_ZAF</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="12" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>126</v>
       </c>
@@ -4083,8 +4352,35 @@
       <c r="X12" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG12" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>762</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>439</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM12" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w131625968-400_ZAF</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO12" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w131625968-400_ZAF</v>
+      </c>
+      <c r="AP12">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="13" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>127</v>
       </c>
@@ -4133,8 +4429,35 @@
       <c r="X13" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG13" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>808</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>807</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM13" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w142414070-400_ZAF</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO13" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w142414070-400_ZAF</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>128</v>
       </c>
@@ -4183,8 +4506,35 @@
       <c r="X14" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG14" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>805</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>723</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM14" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w142414070-765_ZAF</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO14" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w142414070-765_ZAF</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="15" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>129</v>
       </c>
@@ -4233,8 +4583,35 @@
       <c r="X15" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
+      <c r="AG15" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>822</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>735</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM15" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w156418705-400_ZAF</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO15" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w156418705-400_ZAF</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="16" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>130</v>
       </c>
@@ -4283,8 +4660,35 @@
       <c r="X16" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG16" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>752</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM16" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w169647963-400_ZAF</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO16" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w169647963-400_ZAF</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="17" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>131</v>
       </c>
@@ -4333,8 +4737,35 @@
       <c r="X17" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG17" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>353</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM17" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w169789536-400_ZAF</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO17" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w169789536-400_ZAF</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="18" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>132</v>
       </c>
@@ -4383,8 +4814,35 @@
       <c r="X18" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG18" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>767</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>453</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM18" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w179140081-400_ZAF</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO18" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w179140081-400_ZAF</v>
+      </c>
+      <c r="AP18">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>133</v>
       </c>
@@ -4433,8 +4891,35 @@
       <c r="X19" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG19" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>748</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>747</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM19" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w182042518-400_ZAF</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO19" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w182042518-400_ZAF</v>
+      </c>
+      <c r="AP19">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="20" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>134</v>
       </c>
@@ -4483,8 +4968,35 @@
       <c r="X20" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG20" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>789</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>607</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM20" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w182408147-400_ZAF</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO20" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w182408147-400_ZAF</v>
+      </c>
+      <c r="AP20">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="21" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>135</v>
       </c>
@@ -4533,8 +5045,35 @@
       <c r="X21" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG21" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>773</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>495</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM21" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w185171518-400_ZAF</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO21" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w185171518-400_ZAF</v>
+      </c>
+      <c r="AP21">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="22" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>136</v>
       </c>
@@ -4583,8 +5122,35 @@
       <c r="X22" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG22" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>779</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>537</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM22" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w185497473-400_ZAF</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO22" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w185497473-400_ZAF</v>
+      </c>
+      <c r="AP22">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="23" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>137</v>
       </c>
@@ -4633,8 +5199,35 @@
       <c r="X23" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG23" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>793</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>635</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM23" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w200232961-400_ZAF</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO23" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w200232961-400_ZAF</v>
+      </c>
+      <c r="AP23">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="24" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>138</v>
       </c>
@@ -4683,8 +5276,35 @@
       <c r="X24" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG24" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>803</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>705</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM24" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w209365700-400_ZAF</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO24" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w209365700-400_ZAF</v>
+      </c>
+      <c r="AP24">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="25" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>139</v>
       </c>
@@ -4733,8 +5353,35 @@
       <c r="X25" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG25" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>777</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM25" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w209976655-400_ZAF</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO25" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w209976655-400_ZAF</v>
+      </c>
+      <c r="AP25">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="26" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>140</v>
       </c>
@@ -4783,8 +5430,35 @@
       <c r="X26" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG26" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>787</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>593</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM26" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w213181313-400_ZAF</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO26" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w213181313-400_ZAF</v>
+      </c>
+      <c r="AP26">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="27" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>141</v>
       </c>
@@ -4833,8 +5507,35 @@
       <c r="X27" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG27" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>769</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM27" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w220129604-400_ZAF</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO27" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w220129604-400_ZAF</v>
+      </c>
+      <c r="AP27">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="28" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>142</v>
       </c>
@@ -4883,8 +5584,35 @@
       <c r="X28" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG28" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>771</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>481</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM28" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w238322344-400_ZAF</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO28" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w238322344-400_ZAF</v>
+      </c>
+      <c r="AP28">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="29" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>143</v>
       </c>
@@ -4933,8 +5661,35 @@
       <c r="X29" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG29" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>811</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>810</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM29" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w260486370-400_ZAF</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO29" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w260486370-400_ZAF</v>
+      </c>
+      <c r="AP29">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="30" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>144</v>
       </c>
@@ -4983,8 +5738,35 @@
       <c r="X30" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG30" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>797</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>663</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM30" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w455498147-400_ZAF</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO30" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w455498147-400_ZAF</v>
+      </c>
+      <c r="AP30">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="31" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>145</v>
       </c>
@@ -5033,8 +5815,35 @@
       <c r="X31" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG31" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>745</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>346</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM31" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w62193952-400_ZAF</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO31" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w62193952-400_ZAF</v>
+      </c>
+      <c r="AP31">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="32" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>146</v>
       </c>
@@ -5083,8 +5892,35 @@
       <c r="X32" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG32" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>824</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>739</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM32" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w631673098-400_ZAF</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO32" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w631673098-400_ZAF</v>
+      </c>
+      <c r="AP32">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>147</v>
       </c>
@@ -5133,8 +5969,35 @@
       <c r="X33" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG33" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>791</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>621</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM33" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w65600948-400_ZAF</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO33" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w65600948-400_ZAF</v>
+      </c>
+      <c r="AP33">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="34" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>148</v>
       </c>
@@ -5183,8 +6046,35 @@
       <c r="X34" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG34" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>760</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>425</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM34" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w83525879-400_ZAF</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO34" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w83525879-400_ZAF</v>
+      </c>
+      <c r="AP34">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="35" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>149</v>
       </c>
@@ -5233,8 +6123,35 @@
       <c r="X35" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG35" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>743</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>356</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM35" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w836844162-400_ZAF</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO35" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w836844162-400_ZAF</v>
+      </c>
+      <c r="AP35">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="36" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>150</v>
       </c>
@@ -5283,8 +6200,35 @@
       <c r="X36" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG36" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>775</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>509</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM36" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_w98231311-400_ZAF</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO36" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w98231311-400_ZAF</v>
+      </c>
+      <c r="AP36">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="37" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>151</v>
       </c>
@@ -5333,8 +6277,35 @@
       <c r="X37" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG37" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>799</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>677</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM37" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_ZA14-400_ZAF</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO37" t="str">
+        <f t="shared" si="1"/>
+        <v>e_ZA14-400_ZAF</v>
+      </c>
+      <c r="AP37">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="38" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>152</v>
       </c>
@@ -5383,8 +6354,35 @@
       <c r="X38" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG38" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>801</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>691</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM38" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_ZA15-400_ZAF</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO38" t="str">
+        <f t="shared" si="1"/>
+        <v>e_ZA15-400_ZAF</v>
+      </c>
+      <c r="AP38">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="39" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>153</v>
       </c>
@@ -5433,8 +6431,35 @@
       <c r="X39" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG39" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>783</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>565</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM39" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_ZA18-400_ZAF</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO39" t="str">
+        <f t="shared" si="1"/>
+        <v>e_ZA18-400_ZAF</v>
+      </c>
+      <c r="AP39">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="40" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>154</v>
       </c>
@@ -5459,8 +6484,35 @@
       <c r="X40" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG40" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>781</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>551</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM40" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_ZA22-400_ZAF</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO40" t="str">
+        <f t="shared" si="1"/>
+        <v>e_ZA22-400_ZAF</v>
+      </c>
+      <c r="AP40">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="41" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>155</v>
       </c>
@@ -5485,8 +6537,35 @@
       <c r="X41" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG41" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>795</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>649</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM41" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_ZA2-400_ZAF</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO41" t="str">
+        <f t="shared" si="1"/>
+        <v>e_ZA2-400_ZAF</v>
+      </c>
+      <c r="AP41">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="42" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>156</v>
       </c>
@@ -5511,8 +6590,35 @@
       <c r="X42" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG42" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>818</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>727</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM42" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG4hbNREL_ZA26-400_ZAF</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO42" t="str">
+        <f t="shared" si="1"/>
+        <v>e_ZA26-400_ZAF</v>
+      </c>
+      <c r="AP42">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="43" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>157</v>
       </c>
@@ -5537,8 +6643,35 @@
       <c r="X43" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG43" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>763</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>764</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM43" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_r17287657-400_ZAF</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO43" t="str">
+        <f t="shared" si="1"/>
+        <v>e_r17287657-400_ZAF</v>
+      </c>
+      <c r="AP43">
+        <f>8/24</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="44" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>158</v>
       </c>
@@ -5563,8 +6696,35 @@
       <c r="X44" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG44" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>819</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>731</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM44" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w102682082-400_ZAF</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO44" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w102682082-400_ZAF</v>
+      </c>
+      <c r="AP44">
+        <f t="shared" ref="AP44:AP81" si="3">8/24</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="45" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>159</v>
       </c>
@@ -5589,8 +6749,35 @@
       <c r="X45" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG45" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>812</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>813</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM45" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w102925909-400_ZAF</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO45" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w102925909-400_ZAF</v>
+      </c>
+      <c r="AP45">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="46" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>160</v>
       </c>
@@ -5615,8 +6802,35 @@
       <c r="X46" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG46" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>815</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>719</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM46" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w105759402-400_ZAF</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO46" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w105759402-400_ZAF</v>
+      </c>
+      <c r="AP46">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="47" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>161</v>
       </c>
@@ -5641,8 +6855,35 @@
       <c r="X47" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG47" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>784</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>579</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM47" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w105811523-400_ZAF</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO47" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w105811523-400_ZAF</v>
+      </c>
+      <c r="AP47">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="48" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>162</v>
       </c>
@@ -5667,8 +6908,35 @@
       <c r="X48" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG48" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>749</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM48" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w107391770-400_ZAF</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO48" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w107391770-400_ZAF</v>
+      </c>
+      <c r="AP48">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="49" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>163</v>
       </c>
@@ -5693,8 +6961,35 @@
       <c r="X49" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG49" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>757</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>411</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM49" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w107431792-400_ZAF</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO49" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w107431792-400_ZAF</v>
+      </c>
+      <c r="AP49">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="50" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>164</v>
       </c>
@@ -5719,8 +7014,35 @@
       <c r="X50" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG50" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>755</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>397</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM50" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w120941269-400_ZAF</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO50" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w120941269-400_ZAF</v>
+      </c>
+      <c r="AP50">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="51" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>165</v>
       </c>
@@ -5745,8 +7067,35 @@
       <c r="X51" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG51" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>761</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>439</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM51" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w131625968-400_ZAF</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO51" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w131625968-400_ZAF</v>
+      </c>
+      <c r="AP51">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="52" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>166</v>
       </c>
@@ -5771,8 +7120,35 @@
       <c r="X52" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG52" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>806</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>807</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM52" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w142414070-400_ZAF</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO52" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w142414070-400_ZAF</v>
+      </c>
+      <c r="AP52">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="53" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>167</v>
       </c>
@@ -5797,8 +7173,35 @@
       <c r="X53" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG53" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>804</v>
+      </c>
+      <c r="AI53" t="s">
+        <v>723</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM53" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w142414070-765_ZAF</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO53" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w142414070-765_ZAF</v>
+      </c>
+      <c r="AP53">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="54" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>168</v>
       </c>
@@ -5823,8 +7226,35 @@
       <c r="X54" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG54" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH54" t="s">
+        <v>821</v>
+      </c>
+      <c r="AI54" t="s">
+        <v>735</v>
+      </c>
+      <c r="AJ54" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM54" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w156418705-400_ZAF</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO54" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w156418705-400_ZAF</v>
+      </c>
+      <c r="AP54">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="55" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>169</v>
       </c>
@@ -5849,8 +7279,35 @@
       <c r="X55" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG55" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>751</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ55" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM55" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w169647963-400_ZAF</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO55" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w169647963-400_ZAF</v>
+      </c>
+      <c r="AP55">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="56" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>170</v>
       </c>
@@ -5875,8 +7332,35 @@
       <c r="X56" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG56" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>753</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>353</v>
+      </c>
+      <c r="AJ56" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM56" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w169789536-400_ZAF</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO56" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w169789536-400_ZAF</v>
+      </c>
+      <c r="AP56">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="57" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>171</v>
       </c>
@@ -5901,8 +7385,35 @@
       <c r="X57" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG57" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH57" t="s">
+        <v>766</v>
+      </c>
+      <c r="AI57" t="s">
+        <v>453</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM57" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w179140081-400_ZAF</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO57" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w179140081-400_ZAF</v>
+      </c>
+      <c r="AP57">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="58" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>172</v>
       </c>
@@ -5927,8 +7438,35 @@
       <c r="X58" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG58" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH58" t="s">
+        <v>746</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>747</v>
+      </c>
+      <c r="AJ58" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM58" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w182042518-400_ZAF</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO58" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w182042518-400_ZAF</v>
+      </c>
+      <c r="AP58">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="59" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>173</v>
       </c>
@@ -5953,8 +7491,35 @@
       <c r="X59" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG59" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>788</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>607</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM59" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w182408147-400_ZAF</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO59" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w182408147-400_ZAF</v>
+      </c>
+      <c r="AP59">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="60" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>174</v>
       </c>
@@ -5979,8 +7544,35 @@
       <c r="X60" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG60" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>772</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>495</v>
+      </c>
+      <c r="AJ60" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM60" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w185171518-400_ZAF</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO60" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w185171518-400_ZAF</v>
+      </c>
+      <c r="AP60">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="61" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>175</v>
       </c>
@@ -6005,8 +7597,35 @@
       <c r="X61" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG61" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH61" t="s">
+        <v>778</v>
+      </c>
+      <c r="AI61" t="s">
+        <v>537</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM61" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w185497473-400_ZAF</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO61" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w185497473-400_ZAF</v>
+      </c>
+      <c r="AP61">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="62" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>176</v>
       </c>
@@ -6031,8 +7650,35 @@
       <c r="X62" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG62" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH62" t="s">
+        <v>792</v>
+      </c>
+      <c r="AI62" t="s">
+        <v>635</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM62" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w200232961-400_ZAF</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO62" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w200232961-400_ZAF</v>
+      </c>
+      <c r="AP62">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="63" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>177</v>
       </c>
@@ -6057,8 +7703,35 @@
       <c r="X63" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG63" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>802</v>
+      </c>
+      <c r="AI63" t="s">
+        <v>705</v>
+      </c>
+      <c r="AJ63" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM63" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w209365700-400_ZAF</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO63" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w209365700-400_ZAF</v>
+      </c>
+      <c r="AP63">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="64" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>178</v>
       </c>
@@ -6083,8 +7756,35 @@
       <c r="X64" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG64" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>776</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>523</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM64" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w209976655-400_ZAF</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO64" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w209976655-400_ZAF</v>
+      </c>
+      <c r="AP64">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="65" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>179</v>
       </c>
@@ -6109,8 +7809,35 @@
       <c r="X65" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG65" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>786</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>593</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM65" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w213181313-400_ZAF</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO65" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w213181313-400_ZAF</v>
+      </c>
+      <c r="AP65">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="66" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>180</v>
       </c>
@@ -6135,8 +7862,35 @@
       <c r="X66" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG66" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>768</v>
+      </c>
+      <c r="AI66" t="s">
+        <v>467</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM66" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w220129604-400_ZAF</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO66" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w220129604-400_ZAF</v>
+      </c>
+      <c r="AP66">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="67" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>181</v>
       </c>
@@ -6161,8 +7915,35 @@
       <c r="X67" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG67" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>770</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>481</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM67" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w238322344-400_ZAF</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO67" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w238322344-400_ZAF</v>
+      </c>
+      <c r="AP67">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="68" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>182</v>
       </c>
@@ -6187,8 +7968,35 @@
       <c r="X68" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG68" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>809</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>810</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM68" t="str">
+        <f t="shared" si="0"/>
+        <v>EN_STG8hbNREL_w260486370-400_ZAF</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO68" t="str">
+        <f t="shared" si="1"/>
+        <v>e_w260486370-400_ZAF</v>
+      </c>
+      <c r="AP68">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="69" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>183</v>
       </c>
@@ -6213,8 +8021,35 @@
       <c r="X69" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG69" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>796</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>663</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM69" t="str">
+        <f t="shared" ref="AM69:AM81" si="4">AH69</f>
+        <v>EN_STG8hbNREL_w455498147-400_ZAF</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO69" t="str">
+        <f t="shared" ref="AO69:AO81" si="5">AI69</f>
+        <v>e_w455498147-400_ZAF</v>
+      </c>
+      <c r="AP69">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="70" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>184</v>
       </c>
@@ -6239,8 +8074,35 @@
       <c r="X70" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG70" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>744</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>346</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM70" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_w62193952-400_ZAF</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO70" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w62193952-400_ZAF</v>
+      </c>
+      <c r="AP70">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="71" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>185</v>
       </c>
@@ -6265,8 +8127,35 @@
       <c r="X71" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG71" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>823</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>739</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM71" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_w631673098-400_ZAF</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO71" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w631673098-400_ZAF</v>
+      </c>
+      <c r="AP71">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="72" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>186</v>
       </c>
@@ -6291,8 +8180,35 @@
       <c r="X72" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG72" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>790</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>621</v>
+      </c>
+      <c r="AJ72" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM72" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_w65600948-400_ZAF</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO72" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w65600948-400_ZAF</v>
+      </c>
+      <c r="AP72">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="73" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>187</v>
       </c>
@@ -6317,8 +8233,35 @@
       <c r="X73" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG73" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH73" t="s">
+        <v>759</v>
+      </c>
+      <c r="AI73" t="s">
+        <v>425</v>
+      </c>
+      <c r="AJ73" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM73" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_w83525879-400_ZAF</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO73" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w83525879-400_ZAF</v>
+      </c>
+      <c r="AP73">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="74" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>188</v>
       </c>
@@ -6343,8 +8286,35 @@
       <c r="X74" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG74" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH74" t="s">
+        <v>742</v>
+      </c>
+      <c r="AI74" t="s">
+        <v>356</v>
+      </c>
+      <c r="AJ74" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM74" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_w836844162-400_ZAF</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO74" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w836844162-400_ZAF</v>
+      </c>
+      <c r="AP74">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="75" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>189</v>
       </c>
@@ -6369,8 +8339,35 @@
       <c r="X75" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG75" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH75" t="s">
+        <v>774</v>
+      </c>
+      <c r="AI75" t="s">
+        <v>509</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM75" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_w98231311-400_ZAF</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO75" t="str">
+        <f t="shared" si="5"/>
+        <v>e_w98231311-400_ZAF</v>
+      </c>
+      <c r="AP75">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="76" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>190</v>
       </c>
@@ -6395,8 +8392,35 @@
       <c r="X76" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG76" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>798</v>
+      </c>
+      <c r="AI76" t="s">
+        <v>677</v>
+      </c>
+      <c r="AJ76" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM76" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_ZA14-400_ZAF</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO76" t="str">
+        <f t="shared" si="5"/>
+        <v>e_ZA14-400_ZAF</v>
+      </c>
+      <c r="AP76">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>191</v>
       </c>
@@ -6421,8 +8445,35 @@
       <c r="X77" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG77" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH77" t="s">
+        <v>800</v>
+      </c>
+      <c r="AI77" t="s">
+        <v>691</v>
+      </c>
+      <c r="AJ77" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM77" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_ZA15-400_ZAF</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO77" t="str">
+        <f t="shared" si="5"/>
+        <v>e_ZA15-400_ZAF</v>
+      </c>
+      <c r="AP77">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="78" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>192</v>
       </c>
@@ -6447,8 +8498,35 @@
       <c r="X78" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG78" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH78" t="s">
+        <v>782</v>
+      </c>
+      <c r="AI78" t="s">
+        <v>565</v>
+      </c>
+      <c r="AJ78" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM78" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_ZA18-400_ZAF</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO78" t="str">
+        <f t="shared" si="5"/>
+        <v>e_ZA18-400_ZAF</v>
+      </c>
+      <c r="AP78">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="79" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>193</v>
       </c>
@@ -6473,8 +8551,35 @@
       <c r="X79" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG79" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH79" t="s">
+        <v>780</v>
+      </c>
+      <c r="AI79" t="s">
+        <v>551</v>
+      </c>
+      <c r="AJ79" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM79" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_ZA22-400_ZAF</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO79" t="str">
+        <f t="shared" si="5"/>
+        <v>e_ZA22-400_ZAF</v>
+      </c>
+      <c r="AP79">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="80" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>194</v>
       </c>
@@ -6499,8 +8604,35 @@
       <c r="X80" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="81" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG80" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH80" t="s">
+        <v>794</v>
+      </c>
+      <c r="AI80" t="s">
+        <v>649</v>
+      </c>
+      <c r="AJ80" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM80" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_ZA2-400_ZAF</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO80" t="str">
+        <f t="shared" si="5"/>
+        <v>e_ZA2-400_ZAF</v>
+      </c>
+      <c r="AP80">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="81" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>195</v>
       </c>
@@ -6525,8 +8657,35 @@
       <c r="X81" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="82" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="AG81" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>817</v>
+      </c>
+      <c r="AI81" t="s">
+        <v>727</v>
+      </c>
+      <c r="AJ81" t="s">
+        <v>357</v>
+      </c>
+      <c r="AM81" t="str">
+        <f t="shared" si="4"/>
+        <v>EN_STG8hbNREL_ZA26-400_ZAF</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>946</v>
+      </c>
+      <c r="AO81" t="str">
+        <f t="shared" si="5"/>
+        <v>e_ZA26-400_ZAF</v>
+      </c>
+      <c r="AP81">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="82" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>196</v>
       </c>
@@ -6552,7 +8711,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="83" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>197</v>
       </c>
@@ -6578,7 +8737,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="84" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>198</v>
       </c>
@@ -6604,7 +8763,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="85" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>199</v>
       </c>
@@ -6630,7 +8789,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="86" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
         <v>200</v>
       </c>
@@ -6656,7 +8815,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="87" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
         <v>201</v>
       </c>
@@ -6682,7 +8841,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="88" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
         <v>202</v>
       </c>
@@ -6708,7 +8867,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="89" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
         <v>203</v>
       </c>
@@ -6734,7 +8893,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="90" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
         <v>204</v>
       </c>
@@ -6760,7 +8919,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="91" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
         <v>205</v>
       </c>
@@ -6786,7 +8945,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="92" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
         <v>206</v>
       </c>
@@ -6812,7 +8971,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="93" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
         <v>207</v>
       </c>
@@ -6838,7 +8997,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="94" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
         <v>208</v>
       </c>
@@ -6864,7 +9023,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="95" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
         <v>209</v>
       </c>
@@ -6890,7 +9049,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="96" spans="2:24" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:42" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
         <v>210</v>
       </c>
@@ -11677,7 +13836,7 @@
         <v>356</v>
       </c>
       <c r="X360" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="361" spans="21:24" x14ac:dyDescent="0.45">
@@ -11691,7 +13850,7 @@
         <v>356</v>
       </c>
       <c r="X361" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="362" spans="21:24" x14ac:dyDescent="0.45">
@@ -11705,7 +13864,7 @@
         <v>346</v>
       </c>
       <c r="X362" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="363" spans="21:24" x14ac:dyDescent="0.45">
@@ -11719,7 +13878,7 @@
         <v>346</v>
       </c>
       <c r="X363" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="364" spans="21:24" x14ac:dyDescent="0.45">
@@ -11733,7 +13892,7 @@
         <v>747</v>
       </c>
       <c r="X364" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="365" spans="21:24" x14ac:dyDescent="0.45">
@@ -11747,7 +13906,7 @@
         <v>747</v>
       </c>
       <c r="X365" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="366" spans="21:24" x14ac:dyDescent="0.45">
@@ -11761,7 +13920,7 @@
         <v>347</v>
       </c>
       <c r="X366" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="367" spans="21:24" x14ac:dyDescent="0.45">
@@ -11775,7 +13934,7 @@
         <v>347</v>
       </c>
       <c r="X367" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="368" spans="21:24" x14ac:dyDescent="0.45">
@@ -11789,7 +13948,7 @@
         <v>348</v>
       </c>
       <c r="X368" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="369" spans="21:24" x14ac:dyDescent="0.45">
@@ -11803,7 +13962,7 @@
         <v>348</v>
       </c>
       <c r="X369" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="370" spans="21:24" x14ac:dyDescent="0.45">
@@ -11817,7 +13976,7 @@
         <v>353</v>
       </c>
       <c r="X370" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="371" spans="21:24" x14ac:dyDescent="0.45">
@@ -11831,7 +13990,7 @@
         <v>353</v>
       </c>
       <c r="X371" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="372" spans="21:24" x14ac:dyDescent="0.45">
@@ -11845,7 +14004,7 @@
         <v>397</v>
       </c>
       <c r="X372" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="373" spans="21:24" x14ac:dyDescent="0.45">
@@ -11859,7 +14018,7 @@
         <v>397</v>
       </c>
       <c r="X373" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="374" spans="21:24" x14ac:dyDescent="0.45">
@@ -11873,7 +14032,7 @@
         <v>411</v>
       </c>
       <c r="X374" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="375" spans="21:24" x14ac:dyDescent="0.45">
@@ -11887,7 +14046,7 @@
         <v>411</v>
       </c>
       <c r="X375" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="376" spans="21:24" x14ac:dyDescent="0.45">
@@ -11901,7 +14060,7 @@
         <v>425</v>
       </c>
       <c r="X376" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="377" spans="21:24" x14ac:dyDescent="0.45">
@@ -11915,7 +14074,7 @@
         <v>425</v>
       </c>
       <c r="X377" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="378" spans="21:24" x14ac:dyDescent="0.45">
@@ -11929,7 +14088,7 @@
         <v>439</v>
       </c>
       <c r="X378" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="379" spans="21:24" x14ac:dyDescent="0.45">
@@ -11943,7 +14102,7 @@
         <v>439</v>
       </c>
       <c r="X379" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="380" spans="21:24" x14ac:dyDescent="0.45">
@@ -11957,7 +14116,7 @@
         <v>764</v>
       </c>
       <c r="X380" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="381" spans="21:24" x14ac:dyDescent="0.45">
@@ -11971,7 +14130,7 @@
         <v>764</v>
       </c>
       <c r="X381" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="382" spans="21:24" x14ac:dyDescent="0.45">
@@ -11985,7 +14144,7 @@
         <v>453</v>
       </c>
       <c r="X382" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="383" spans="21:24" x14ac:dyDescent="0.45">
@@ -11999,7 +14158,7 @@
         <v>453</v>
       </c>
       <c r="X383" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="384" spans="21:24" x14ac:dyDescent="0.45">
@@ -12013,7 +14172,7 @@
         <v>467</v>
       </c>
       <c r="X384" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="385" spans="21:24" x14ac:dyDescent="0.45">
@@ -12027,7 +14186,7 @@
         <v>467</v>
       </c>
       <c r="X385" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="386" spans="21:24" x14ac:dyDescent="0.45">
@@ -12041,7 +14200,7 @@
         <v>481</v>
       </c>
       <c r="X386" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="387" spans="21:24" x14ac:dyDescent="0.45">
@@ -12055,7 +14214,7 @@
         <v>481</v>
       </c>
       <c r="X387" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="388" spans="21:24" x14ac:dyDescent="0.45">
@@ -12069,7 +14228,7 @@
         <v>495</v>
       </c>
       <c r="X388" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="389" spans="21:24" x14ac:dyDescent="0.45">
@@ -12083,7 +14242,7 @@
         <v>495</v>
       </c>
       <c r="X389" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="390" spans="21:24" x14ac:dyDescent="0.45">
@@ -12097,7 +14256,7 @@
         <v>509</v>
       </c>
       <c r="X390" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="391" spans="21:24" x14ac:dyDescent="0.45">
@@ -12111,7 +14270,7 @@
         <v>509</v>
       </c>
       <c r="X391" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="392" spans="21:24" x14ac:dyDescent="0.45">
@@ -12125,7 +14284,7 @@
         <v>523</v>
       </c>
       <c r="X392" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="393" spans="21:24" x14ac:dyDescent="0.45">
@@ -12139,7 +14298,7 @@
         <v>523</v>
       </c>
       <c r="X393" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="394" spans="21:24" x14ac:dyDescent="0.45">
@@ -12153,7 +14312,7 @@
         <v>537</v>
       </c>
       <c r="X394" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="395" spans="21:24" x14ac:dyDescent="0.45">
@@ -12167,7 +14326,7 @@
         <v>537</v>
       </c>
       <c r="X395" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="396" spans="21:24" x14ac:dyDescent="0.45">
@@ -12181,7 +14340,7 @@
         <v>551</v>
       </c>
       <c r="X396" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="397" spans="21:24" x14ac:dyDescent="0.45">
@@ -12195,7 +14354,7 @@
         <v>551</v>
       </c>
       <c r="X397" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="398" spans="21:24" x14ac:dyDescent="0.45">
@@ -12209,7 +14368,7 @@
         <v>565</v>
       </c>
       <c r="X398" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="399" spans="21:24" x14ac:dyDescent="0.45">
@@ -12223,7 +14382,7 @@
         <v>565</v>
       </c>
       <c r="X399" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="400" spans="21:24" x14ac:dyDescent="0.45">
@@ -12237,7 +14396,7 @@
         <v>579</v>
       </c>
       <c r="X400" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="401" spans="21:24" x14ac:dyDescent="0.45">
@@ -12251,7 +14410,7 @@
         <v>579</v>
       </c>
       <c r="X401" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="402" spans="21:24" x14ac:dyDescent="0.45">
@@ -12265,7 +14424,7 @@
         <v>593</v>
       </c>
       <c r="X402" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="403" spans="21:24" x14ac:dyDescent="0.45">
@@ -12279,7 +14438,7 @@
         <v>593</v>
       </c>
       <c r="X403" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="404" spans="21:24" x14ac:dyDescent="0.45">
@@ -12293,7 +14452,7 @@
         <v>607</v>
       </c>
       <c r="X404" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="405" spans="21:24" x14ac:dyDescent="0.45">
@@ -12307,7 +14466,7 @@
         <v>607</v>
       </c>
       <c r="X405" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="406" spans="21:24" x14ac:dyDescent="0.45">
@@ -12321,7 +14480,7 @@
         <v>621</v>
       </c>
       <c r="X406" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="407" spans="21:24" x14ac:dyDescent="0.45">
@@ -12335,7 +14494,7 @@
         <v>621</v>
       </c>
       <c r="X407" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="408" spans="21:24" x14ac:dyDescent="0.45">
@@ -12349,7 +14508,7 @@
         <v>635</v>
       </c>
       <c r="X408" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="409" spans="21:24" x14ac:dyDescent="0.45">
@@ -12363,7 +14522,7 @@
         <v>635</v>
       </c>
       <c r="X409" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="410" spans="21:24" x14ac:dyDescent="0.45">
@@ -12377,7 +14536,7 @@
         <v>649</v>
       </c>
       <c r="X410" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="411" spans="21:24" x14ac:dyDescent="0.45">
@@ -12391,7 +14550,7 @@
         <v>649</v>
       </c>
       <c r="X411" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="412" spans="21:24" x14ac:dyDescent="0.45">
@@ -12405,7 +14564,7 @@
         <v>663</v>
       </c>
       <c r="X412" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="413" spans="21:24" x14ac:dyDescent="0.45">
@@ -12419,7 +14578,7 @@
         <v>663</v>
       </c>
       <c r="X413" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="414" spans="21:24" x14ac:dyDescent="0.45">
@@ -12433,7 +14592,7 @@
         <v>677</v>
       </c>
       <c r="X414" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="415" spans="21:24" x14ac:dyDescent="0.45">
@@ -12447,7 +14606,7 @@
         <v>677</v>
       </c>
       <c r="X415" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="416" spans="21:24" x14ac:dyDescent="0.45">
@@ -12461,7 +14620,7 @@
         <v>691</v>
       </c>
       <c r="X416" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="417" spans="21:24" x14ac:dyDescent="0.45">
@@ -12475,7 +14634,7 @@
         <v>691</v>
       </c>
       <c r="X417" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="418" spans="21:24" x14ac:dyDescent="0.45">
@@ -12489,7 +14648,7 @@
         <v>705</v>
       </c>
       <c r="X418" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="419" spans="21:24" x14ac:dyDescent="0.45">
@@ -12503,7 +14662,7 @@
         <v>705</v>
       </c>
       <c r="X419" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="420" spans="21:24" x14ac:dyDescent="0.45">
@@ -12517,7 +14676,7 @@
         <v>723</v>
       </c>
       <c r="X420" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="421" spans="21:24" x14ac:dyDescent="0.45">
@@ -12531,7 +14690,7 @@
         <v>723</v>
       </c>
       <c r="X421" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="422" spans="21:24" x14ac:dyDescent="0.45">
@@ -12545,7 +14704,7 @@
         <v>807</v>
       </c>
       <c r="X422" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="423" spans="21:24" x14ac:dyDescent="0.45">
@@ -12559,7 +14718,7 @@
         <v>807</v>
       </c>
       <c r="X423" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="424" spans="21:24" x14ac:dyDescent="0.45">
@@ -12573,7 +14732,7 @@
         <v>810</v>
       </c>
       <c r="X424" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="425" spans="21:24" x14ac:dyDescent="0.45">
@@ -12587,7 +14746,7 @@
         <v>810</v>
       </c>
       <c r="X425" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="426" spans="21:24" x14ac:dyDescent="0.45">
@@ -12601,7 +14760,7 @@
         <v>813</v>
       </c>
       <c r="X426" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="427" spans="21:24" x14ac:dyDescent="0.45">
@@ -12615,7 +14774,7 @@
         <v>813</v>
       </c>
       <c r="X427" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="428" spans="21:24" x14ac:dyDescent="0.45">
@@ -12629,7 +14788,7 @@
         <v>719</v>
       </c>
       <c r="X428" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="429" spans="21:24" x14ac:dyDescent="0.45">
@@ -12643,7 +14802,7 @@
         <v>719</v>
       </c>
       <c r="X429" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="430" spans="21:24" x14ac:dyDescent="0.45">
@@ -12657,7 +14816,7 @@
         <v>727</v>
       </c>
       <c r="X430" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="431" spans="21:24" x14ac:dyDescent="0.45">
@@ -12671,7 +14830,7 @@
         <v>727</v>
       </c>
       <c r="X431" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="432" spans="21:24" x14ac:dyDescent="0.45">
@@ -12685,7 +14844,7 @@
         <v>731</v>
       </c>
       <c r="X432" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="433" spans="21:24" x14ac:dyDescent="0.45">
@@ -12699,7 +14858,7 @@
         <v>731</v>
       </c>
       <c r="X433" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="434" spans="21:24" x14ac:dyDescent="0.45">
@@ -12713,7 +14872,7 @@
         <v>735</v>
       </c>
       <c r="X434" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="435" spans="21:24" x14ac:dyDescent="0.45">
@@ -12727,7 +14886,7 @@
         <v>735</v>
       </c>
       <c r="X435" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="436" spans="21:24" x14ac:dyDescent="0.45">
@@ -12741,7 +14900,7 @@
         <v>739</v>
       </c>
       <c r="X436" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="437" spans="21:24" x14ac:dyDescent="0.45">
@@ -12755,10 +14914,13 @@
         <v>739</v>
       </c>
       <c r="X437" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AH4:AJ81">
+    <sortCondition ref="AH4:AH81"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5032E83-30B0-48EB-A451-C20EEB42ACED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F9214-3A19-4FEE-A89E-4533266874C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -3822,7 +3822,7 @@
         <v>e_w102682082-400_ZAF</v>
       </c>
       <c r="AP5">
-        <f t="shared" ref="AP5:AP68" si="2">4/24</f>
+        <f t="shared" ref="AP5:AP42" si="2">4/24</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -18866,7 +18866,7 @@
         <v>42</v>
       </c>
       <c r="E27">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F27" t="str">
         <f>C27</f>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F9214-3A19-4FEE-A89E-4533266874C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938B5C5E-DF89-484E-8B8B-C22C73258BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4284" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4390" uniqueCount="950">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2979,6 +2979,9 @@
   </si>
   <si>
     <t>~TFM_DINS-AT</t>
+  </si>
+  <si>
+    <t>ELE</t>
   </si>
 </sst>
 </file>
@@ -14927,7 +14930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8E1348-6DD1-4555-B7B4-7AB70C2A26E6}">
-  <dimension ref="B1:I109"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -14939,12 +14942,12 @@
     <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C1" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C3" t="s">
         <v>37</v>
       </c>
@@ -14952,7 +14955,10 @@
         <v>838</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>831</v>
+      </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
@@ -14975,7 +14981,10 @@
         <v>839</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>949</v>
+      </c>
       <c r="B5" t="str">
         <f>"UCE_elcagg_"&amp;MID(C5,5,32)</f>
         <v>UCE_elcagg_spv_ZAF_001</v>
@@ -15001,7 +15010,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>949</v>
+      </c>
       <c r="B6" t="str">
         <f t="shared" ref="B6:B69" si="0">"UCE_elcagg_"&amp;MID(C6,5,32)</f>
         <v>UCE_elcagg_spv_ZAF_002</v>
@@ -15027,7 +15039,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>949</v>
+      </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_003</v>
@@ -15053,7 +15068,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>949</v>
+      </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_004</v>
@@ -15079,7 +15097,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>949</v>
+      </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_005</v>
@@ -15105,7 +15126,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>949</v>
+      </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_006</v>
@@ -15131,7 +15155,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>949</v>
+      </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_007</v>
@@ -15157,7 +15184,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>949</v>
+      </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_008</v>
@@ -15183,7 +15213,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>949</v>
+      </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_009</v>
@@ -15209,7 +15242,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>949</v>
+      </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_010</v>
@@ -15235,7 +15271,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>949</v>
+      </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_011</v>
@@ -15261,7 +15300,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>949</v>
+      </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_012</v>
@@ -15287,7 +15329,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>949</v>
+      </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_013</v>
@@ -15313,7 +15358,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>949</v>
+      </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_014</v>
@@ -15339,7 +15387,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>949</v>
+      </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_015</v>
@@ -15365,7 +15416,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>949</v>
+      </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_016</v>
@@ -15391,7 +15445,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>949</v>
+      </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_017</v>
@@ -15417,7 +15474,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>949</v>
+      </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_018</v>
@@ -15443,7 +15503,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>949</v>
+      </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_019</v>
@@ -15469,7 +15532,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>949</v>
+      </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_020</v>
@@ -15495,7 +15561,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>949</v>
+      </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_021</v>
@@ -15521,7 +15590,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>949</v>
+      </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_022</v>
@@ -15547,7 +15619,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>949</v>
+      </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_023</v>
@@ -15573,7 +15648,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>949</v>
+      </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_024</v>
@@ -15599,7 +15677,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>949</v>
+      </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_025</v>
@@ -15625,7 +15706,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>949</v>
+      </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_026</v>
@@ -15651,7 +15735,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>949</v>
+      </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_027</v>
@@ -15677,7 +15764,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>949</v>
+      </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_028</v>
@@ -15703,7 +15793,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>949</v>
+      </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_029</v>
@@ -15729,7 +15822,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>949</v>
+      </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_030</v>
@@ -15755,7 +15851,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>949</v>
+      </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_031</v>
@@ -15781,7 +15880,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>949</v>
+      </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_032</v>
@@ -15807,7 +15909,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>949</v>
+      </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_033</v>
@@ -15833,7 +15938,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>949</v>
+      </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_034</v>
@@ -15859,7 +15967,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>949</v>
+      </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_035</v>
@@ -15885,7 +15996,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>949</v>
+      </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_036</v>
@@ -15911,7 +16025,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>949</v>
+      </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_037</v>
@@ -15937,7 +16054,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>949</v>
+      </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_038</v>
@@ -15963,7 +16083,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>949</v>
+      </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_039</v>
@@ -15989,7 +16112,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>949</v>
+      </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_040</v>
@@ -16015,7 +16141,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>949</v>
+      </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_041</v>
@@ -16041,7 +16170,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>949</v>
+      </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_042</v>
@@ -16067,7 +16199,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>949</v>
+      </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_spv_ZAF_043</v>
@@ -16093,7 +16228,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>949</v>
+      </c>
       <c r="B48" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_001</v>
@@ -16119,7 +16257,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>949</v>
+      </c>
       <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_002</v>
@@ -16145,7 +16286,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>949</v>
+      </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_003</v>
@@ -16171,7 +16315,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>949</v>
+      </c>
       <c r="B51" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_004</v>
@@ -16197,7 +16344,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>949</v>
+      </c>
       <c r="B52" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_005</v>
@@ -16223,7 +16373,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>949</v>
+      </c>
       <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_006</v>
@@ -16249,7 +16402,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>949</v>
+      </c>
       <c r="B54" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_007</v>
@@ -16275,7 +16431,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>949</v>
+      </c>
       <c r="B55" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_008</v>
@@ -16301,7 +16460,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>949</v>
+      </c>
       <c r="B56" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_009</v>
@@ -16327,7 +16489,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>949</v>
+      </c>
       <c r="B57" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_010</v>
@@ -16353,7 +16518,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>949</v>
+      </c>
       <c r="B58" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_011</v>
@@ -16379,7 +16547,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>949</v>
+      </c>
       <c r="B59" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_012</v>
@@ -16405,7 +16576,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>949</v>
+      </c>
       <c r="B60" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_013</v>
@@ -16431,7 +16605,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>949</v>
+      </c>
       <c r="B61" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_014</v>
@@ -16457,7 +16634,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>949</v>
+      </c>
       <c r="B62" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_015</v>
@@ -16483,7 +16663,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>949</v>
+      </c>
       <c r="B63" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_016</v>
@@ -16509,7 +16692,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>949</v>
+      </c>
       <c r="B64" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_017</v>
@@ -16535,7 +16721,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>949</v>
+      </c>
       <c r="B65" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_018</v>
@@ -16561,7 +16750,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>949</v>
+      </c>
       <c r="B66" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_019</v>
@@ -16587,7 +16779,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>949</v>
+      </c>
       <c r="B67" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_wof_ZAF_020</v>
@@ -16613,7 +16808,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>949</v>
+      </c>
       <c r="B68" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_won_ZAF_001</v>
@@ -16639,7 +16837,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>949</v>
+      </c>
       <c r="B69" t="str">
         <f t="shared" si="0"/>
         <v>UCE_elcagg_won_ZAF_002</v>
@@ -16665,7 +16866,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>949</v>
+      </c>
       <c r="B70" t="str">
         <f t="shared" ref="B70:B109" si="5">"UCE_elcagg_"&amp;MID(C70,5,32)</f>
         <v>UCE_elcagg_won_ZAF_003</v>
@@ -16691,7 +16895,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>949</v>
+      </c>
       <c r="B71" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_004</v>
@@ -16717,7 +16924,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>949</v>
+      </c>
       <c r="B72" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_005</v>
@@ -16743,7 +16953,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>949</v>
+      </c>
       <c r="B73" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_006</v>
@@ -16769,7 +16982,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>949</v>
+      </c>
       <c r="B74" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_007</v>
@@ -16795,7 +17011,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>949</v>
+      </c>
       <c r="B75" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_008</v>
@@ -16821,7 +17040,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>949</v>
+      </c>
       <c r="B76" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_009</v>
@@ -16847,7 +17069,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>949</v>
+      </c>
       <c r="B77" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_010</v>
@@ -16873,7 +17098,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>949</v>
+      </c>
       <c r="B78" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_011</v>
@@ -16899,7 +17127,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>949</v>
+      </c>
       <c r="B79" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_012</v>
@@ -16925,7 +17156,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>949</v>
+      </c>
       <c r="B80" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_013</v>
@@ -16951,7 +17185,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>949</v>
+      </c>
       <c r="B81" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_014</v>
@@ -16977,7 +17214,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>949</v>
+      </c>
       <c r="B82" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_015</v>
@@ -17003,7 +17243,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>949</v>
+      </c>
       <c r="B83" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_016</v>
@@ -17029,7 +17272,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>949</v>
+      </c>
       <c r="B84" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_017</v>
@@ -17055,7 +17301,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>949</v>
+      </c>
       <c r="B85" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_018</v>
@@ -17081,7 +17330,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>949</v>
+      </c>
       <c r="B86" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_019</v>
@@ -17107,7 +17359,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>949</v>
+      </c>
       <c r="B87" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_020</v>
@@ -17133,7 +17388,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>949</v>
+      </c>
       <c r="B88" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_021</v>
@@ -17159,7 +17417,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>949</v>
+      </c>
       <c r="B89" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_022</v>
@@ -17185,7 +17446,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>949</v>
+      </c>
       <c r="B90" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_023</v>
@@ -17211,7 +17475,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>949</v>
+      </c>
       <c r="B91" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_024</v>
@@ -17237,7 +17504,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>949</v>
+      </c>
       <c r="B92" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_025</v>
@@ -17263,7 +17533,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>949</v>
+      </c>
       <c r="B93" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_026</v>
@@ -17289,7 +17562,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>949</v>
+      </c>
       <c r="B94" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_027</v>
@@ -17315,7 +17591,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>949</v>
+      </c>
       <c r="B95" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_028</v>
@@ -17341,7 +17620,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>949</v>
+      </c>
       <c r="B96" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_029</v>
@@ -17367,7 +17649,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>949</v>
+      </c>
       <c r="B97" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_030</v>
@@ -17393,7 +17678,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>949</v>
+      </c>
       <c r="B98" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_031</v>
@@ -17419,7 +17707,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>949</v>
+      </c>
       <c r="B99" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_032</v>
@@ -17445,7 +17736,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>949</v>
+      </c>
       <c r="B100" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_033</v>
@@ -17471,7 +17765,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>949</v>
+      </c>
       <c r="B101" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_034</v>
@@ -17497,7 +17794,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>949</v>
+      </c>
       <c r="B102" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_035</v>
@@ -17523,7 +17823,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>949</v>
+      </c>
       <c r="B103" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_036</v>
@@ -17549,7 +17852,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>949</v>
+      </c>
       <c r="B104" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_037</v>
@@ -17575,7 +17881,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>949</v>
+      </c>
       <c r="B105" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_038</v>
@@ -17601,7 +17910,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>949</v>
+      </c>
       <c r="B106" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_039</v>
@@ -17627,7 +17939,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>949</v>
+      </c>
       <c r="B107" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_040</v>
@@ -17653,7 +17968,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>949</v>
+      </c>
       <c r="B108" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_041</v>
@@ -17679,7 +17997,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>949</v>
+      </c>
       <c r="B109" t="str">
         <f t="shared" si="5"/>
         <v>UCE_elcagg_won_ZAF_042</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC39379-2662-42A2-A43B-C66E1FA05448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C5C8C2-0C13-4F0A-A141-10403B8213A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4390" uniqueCount="950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4407" uniqueCount="954">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2982,6 +2982,18 @@
   </si>
   <si>
     <t>g[_]*,distr*</t>
+  </si>
+  <si>
+    <t>w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>w219384657-765_ZAF</t>
+  </si>
+  <si>
+    <t>w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>w90454383-400_ZAF</t>
   </si>
 </sst>
 </file>
@@ -3531,11 +3543,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA2A-D9BC-41EA-AC3A-70604C608562}">
-  <dimension ref="B2:AP437"/>
+  <dimension ref="B2:AP446"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="21" max="21" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="47.265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="37.9296875" customWidth="1"/>
     <col min="23" max="23" width="20.1328125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="4.06640625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="10.1328125" bestFit="1" customWidth="1"/>
@@ -14850,7 +14862,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="433" spans="21:24" x14ac:dyDescent="0.45">
+    <row r="433" spans="18:24" x14ac:dyDescent="0.45">
       <c r="U433" t="s">
         <v>113</v>
       </c>
@@ -14864,7 +14876,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="434" spans="21:24" x14ac:dyDescent="0.45">
+    <row r="434" spans="18:24" x14ac:dyDescent="0.45">
       <c r="U434" t="s">
         <v>113</v>
       </c>
@@ -14878,7 +14890,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="435" spans="21:24" x14ac:dyDescent="0.45">
+    <row r="435" spans="18:24" x14ac:dyDescent="0.45">
       <c r="U435" t="s">
         <v>113</v>
       </c>
@@ -14892,7 +14904,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="436" spans="21:24" x14ac:dyDescent="0.45">
+    <row r="436" spans="18:24" x14ac:dyDescent="0.45">
       <c r="U436" t="s">
         <v>113</v>
       </c>
@@ -14906,7 +14918,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="437" spans="21:24" x14ac:dyDescent="0.45">
+    <row r="437" spans="18:24" x14ac:dyDescent="0.45">
       <c r="U437" t="s">
         <v>113</v>
       </c>
@@ -14918,6 +14930,101 @@
       </c>
       <c r="X437" t="s">
         <v>344</v>
+      </c>
+    </row>
+    <row r="441" spans="18:24" x14ac:dyDescent="0.45">
+      <c r="U441" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="442" spans="18:24" x14ac:dyDescent="0.45">
+      <c r="U442" t="s">
+        <v>353</v>
+      </c>
+      <c r="V442" t="s">
+        <v>3</v>
+      </c>
+      <c r="W442" t="s">
+        <v>300</v>
+      </c>
+      <c r="X442" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="443" spans="18:24" x14ac:dyDescent="0.45">
+      <c r="R443" t="s">
+        <v>950</v>
+      </c>
+      <c r="U443" t="s">
+        <v>113</v>
+      </c>
+      <c r="V443" t="str">
+        <f>"Nuclear large_"&amp;R443</f>
+        <v>Nuclear large_w836844162-400_ZAF</v>
+      </c>
+      <c r="W443" t="str">
+        <f>"e_"&amp;R443</f>
+        <v>e_w836844162-400_ZAF</v>
+      </c>
+      <c r="X443" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="444" spans="18:24" x14ac:dyDescent="0.45">
+      <c r="R444" t="s">
+        <v>951</v>
+      </c>
+      <c r="U444" t="s">
+        <v>113</v>
+      </c>
+      <c r="V444" t="str">
+        <f t="shared" ref="V444:V446" si="6">"Nuclear large_"&amp;R444</f>
+        <v>Nuclear large_w219384657-765_ZAF</v>
+      </c>
+      <c r="W444" t="str">
+        <f t="shared" ref="W444:W446" si="7">"e_"&amp;R444</f>
+        <v>e_w219384657-765_ZAF</v>
+      </c>
+      <c r="X444" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="445" spans="18:24" x14ac:dyDescent="0.45">
+      <c r="R445" t="s">
+        <v>952</v>
+      </c>
+      <c r="U445" t="s">
+        <v>113</v>
+      </c>
+      <c r="V445" t="str">
+        <f t="shared" si="6"/>
+        <v>Nuclear large_w102682082-400_ZAF</v>
+      </c>
+      <c r="W445" t="str">
+        <f t="shared" si="7"/>
+        <v>e_w102682082-400_ZAF</v>
+      </c>
+      <c r="X445" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="446" spans="18:24" x14ac:dyDescent="0.45">
+      <c r="R446" t="s">
+        <v>953</v>
+      </c>
+      <c r="U446" t="s">
+        <v>113</v>
+      </c>
+      <c r="V446" t="str">
+        <f t="shared" si="6"/>
+        <v>Nuclear large_w90454383-400_ZAF</v>
+      </c>
+      <c r="W446" t="str">
+        <f t="shared" si="7"/>
+        <v>e_w90454383-400_ZAF</v>
+      </c>
+      <c r="X446" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
